--- a/formato/formato_informe_ups.xlsx
+++ b/formato/formato_informe_ups.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CSA Área TI\Documents\CSA\Epicollect\Generacion_informes\formato\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBA94B8-8C80-4504-A2CF-E470DEF4B23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79518D51-572A-402B-B1D4-994EAAC8DE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="727" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="727" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATOS GENERALES" sheetId="1" r:id="rId1"/>
     <sheet name="EVIDENCIA DEL MANTENIMIENTO" sheetId="2" r:id="rId2"/>
-    <sheet name="MEDICIONES DE ENTRADA " sheetId="3" r:id="rId3"/>
+    <sheet name="MEDICIONES DE ENTRADA" sheetId="3" r:id="rId3"/>
     <sheet name="MEDICIONES DE SALIDA" sheetId="4" r:id="rId4"/>
     <sheet name="NOVEDADES" sheetId="5" r:id="rId5"/>
     <sheet name="DATOS" sheetId="6" state="hidden" r:id="rId6"/>
@@ -1996,145 +1996,8 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2172,6 +2035,177 @@
     <xf numFmtId="165" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2184,60 +2218,73 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2251,53 +2298,21 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2335,18 +2350,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2394,9 +2397,6 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3145,410 +3145,410 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="126"/>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="126" t="s">
+      <c r="A1" s="69"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="128"/>
-      <c r="S1" s="126"/>
-      <c r="T1" s="127"/>
-      <c r="U1" s="127"/>
-      <c r="V1" s="127"/>
-      <c r="W1" s="128"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="70"/>
+      <c r="U1" s="70"/>
+      <c r="V1" s="70"/>
+      <c r="W1" s="71"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="129"/>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="130"/>
-      <c r="Q2" s="130"/>
-      <c r="R2" s="131"/>
-      <c r="S2" s="129"/>
-      <c r="T2" s="130"/>
-      <c r="U2" s="130"/>
-      <c r="V2" s="130"/>
-      <c r="W2" s="131"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
+      <c r="W2" s="74"/>
     </row>
     <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="129"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
-      <c r="Q3" s="130"/>
-      <c r="R3" s="131"/>
-      <c r="S3" s="129"/>
-      <c r="T3" s="130"/>
-      <c r="U3" s="130"/>
-      <c r="V3" s="130"/>
-      <c r="W3" s="131"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="74"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="W3" s="74"/>
     </row>
     <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="129"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="130"/>
-      <c r="P4" s="130"/>
-      <c r="Q4" s="130"/>
-      <c r="R4" s="131"/>
-      <c r="S4" s="129"/>
-      <c r="T4" s="130"/>
-      <c r="U4" s="130"/>
-      <c r="V4" s="130"/>
-      <c r="W4" s="131"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="72"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="W4" s="74"/>
     </row>
     <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="129"/>
-      <c r="B5" s="130"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="130"/>
-      <c r="N5" s="130"/>
-      <c r="O5" s="130"/>
-      <c r="P5" s="130"/>
-      <c r="Q5" s="130"/>
-      <c r="R5" s="131"/>
-      <c r="S5" s="129"/>
-      <c r="T5" s="130"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="130"/>
-      <c r="W5" s="131"/>
+      <c r="A5" s="72"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="73"/>
+      <c r="U5" s="73"/>
+      <c r="V5" s="73"/>
+      <c r="W5" s="74"/>
     </row>
     <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="129"/>
-      <c r="B6" s="130"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="130"/>
-      <c r="Q6" s="130"/>
-      <c r="R6" s="131"/>
-      <c r="S6" s="129"/>
-      <c r="T6" s="130"/>
-      <c r="U6" s="130"/>
-      <c r="V6" s="130"/>
-      <c r="W6" s="131"/>
+      <c r="A6" s="72"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="73"/>
+      <c r="Q6" s="73"/>
+      <c r="R6" s="74"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="73"/>
+      <c r="U6" s="73"/>
+      <c r="V6" s="73"/>
+      <c r="W6" s="74"/>
     </row>
     <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="129"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="131"/>
-      <c r="S7" s="129"/>
-      <c r="T7" s="130"/>
-      <c r="U7" s="130"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="131"/>
+      <c r="A7" s="72"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="73"/>
+      <c r="Q7" s="73"/>
+      <c r="R7" s="74"/>
+      <c r="S7" s="72"/>
+      <c r="T7" s="73"/>
+      <c r="U7" s="73"/>
+      <c r="V7" s="73"/>
+      <c r="W7" s="74"/>
     </row>
     <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="132"/>
-      <c r="B8" s="133"/>
-      <c r="C8" s="133"/>
-      <c r="D8" s="133"/>
-      <c r="E8" s="134"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="133"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="133"/>
-      <c r="K8" s="133"/>
-      <c r="L8" s="133"/>
-      <c r="M8" s="133"/>
-      <c r="N8" s="133"/>
-      <c r="O8" s="133"/>
-      <c r="P8" s="133"/>
-      <c r="Q8" s="133"/>
-      <c r="R8" s="134"/>
-      <c r="S8" s="132"/>
-      <c r="T8" s="133"/>
-      <c r="U8" s="133"/>
-      <c r="V8" s="133"/>
-      <c r="W8" s="134"/>
+      <c r="A8" s="75"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="76"/>
+      <c r="N8" s="76"/>
+      <c r="O8" s="76"/>
+      <c r="P8" s="76"/>
+      <c r="Q8" s="76"/>
+      <c r="R8" s="77"/>
+      <c r="S8" s="75"/>
+      <c r="T8" s="76"/>
+      <c r="U8" s="76"/>
+      <c r="V8" s="76"/>
+      <c r="W8" s="77"/>
     </row>
     <row r="9" spans="1:23" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="135"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="136"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="136"/>
-      <c r="J9" s="137"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="80"/>
       <c r="K9" s="2" t="s">
         <v>2</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="138" t="str">
+      <c r="M9" s="81" t="str">
         <f>CONCATENATE("UPS ",F15," "," DE ",J15," KVA")</f>
         <v>UPS   DE  KVA</v>
       </c>
-      <c r="N9" s="136"/>
-      <c r="O9" s="136"/>
-      <c r="P9" s="136"/>
-      <c r="Q9" s="137"/>
+      <c r="N9" s="79"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="79"/>
+      <c r="Q9" s="80"/>
       <c r="R9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="S9" s="139"/>
-      <c r="T9" s="140"/>
-      <c r="U9" s="140"/>
-      <c r="V9" s="140"/>
-      <c r="W9" s="141"/>
+      <c r="S9" s="82"/>
+      <c r="T9" s="83"/>
+      <c r="U9" s="83"/>
+      <c r="V9" s="83"/>
+      <c r="W9" s="84"/>
     </row>
     <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="142"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="77"/>
-      <c r="K10" s="232" t="s">
+      <c r="B10" s="85"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="87"/>
+      <c r="K10" s="65" t="s">
         <v>164</v>
       </c>
-      <c r="L10" s="123"/>
-      <c r="M10" s="124"/>
-      <c r="N10" s="124"/>
-      <c r="O10" s="124"/>
-      <c r="P10" s="124"/>
-      <c r="Q10" s="124"/>
-      <c r="R10" s="124"/>
-      <c r="S10" s="124"/>
-      <c r="T10" s="124"/>
-      <c r="U10" s="124"/>
-      <c r="V10" s="124"/>
-      <c r="W10" s="125"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="67"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="67"/>
+      <c r="V10" s="67"/>
+      <c r="W10" s="68"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="121"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="69" t="s">
+      <c r="B11" s="88"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="87"/>
+      <c r="K11" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="L11" s="77"/>
-      <c r="M11" s="121"/>
-      <c r="N11" s="78"/>
-      <c r="O11" s="78"/>
-      <c r="P11" s="78"/>
-      <c r="Q11" s="78"/>
-      <c r="R11" s="78"/>
-      <c r="S11" s="78"/>
-      <c r="T11" s="78"/>
-      <c r="U11" s="78"/>
-      <c r="V11" s="78"/>
-      <c r="W11" s="79"/>
+      <c r="L11" s="87"/>
+      <c r="M11" s="88"/>
+      <c r="N11" s="86"/>
+      <c r="O11" s="86"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="86"/>
+      <c r="R11" s="86"/>
+      <c r="S11" s="86"/>
+      <c r="T11" s="86"/>
+      <c r="U11" s="86"/>
+      <c r="V11" s="86"/>
+      <c r="W11" s="90"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="121"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="69" t="s">
+      <c r="B12" s="88"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="87"/>
+      <c r="K12" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="L12" s="77"/>
-      <c r="M12" s="121"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="78"/>
-      <c r="P12" s="78"/>
-      <c r="Q12" s="78"/>
-      <c r="R12" s="78"/>
-      <c r="S12" s="78"/>
-      <c r="T12" s="78"/>
-      <c r="U12" s="78"/>
-      <c r="V12" s="78"/>
-      <c r="W12" s="79"/>
+      <c r="L12" s="87"/>
+      <c r="M12" s="88"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="86"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="86"/>
+      <c r="R12" s="86"/>
+      <c r="S12" s="86"/>
+      <c r="T12" s="86"/>
+      <c r="U12" s="86"/>
+      <c r="V12" s="86"/>
+      <c r="W12" s="90"/>
     </row>
     <row r="13" spans="1:23" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="92"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="78"/>
-      <c r="N13" s="78"/>
-      <c r="O13" s="78"/>
-      <c r="P13" s="78"/>
-      <c r="Q13" s="78"/>
-      <c r="R13" s="78"/>
-      <c r="S13" s="78"/>
-      <c r="T13" s="78"/>
-      <c r="U13" s="78"/>
-      <c r="V13" s="78"/>
-      <c r="W13" s="79"/>
+      <c r="A13" s="91"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
+      <c r="M13" s="86"/>
+      <c r="N13" s="86"/>
+      <c r="O13" s="86"/>
+      <c r="P13" s="86"/>
+      <c r="Q13" s="86"/>
+      <c r="R13" s="86"/>
+      <c r="S13" s="86"/>
+      <c r="T13" s="86"/>
+      <c r="U13" s="86"/>
+      <c r="V13" s="86"/>
+      <c r="W13" s="90"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="65" t="s">
+      <c r="A14" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="78"/>
-      <c r="N14" s="78"/>
-      <c r="O14" s="78"/>
-      <c r="P14" s="78"/>
-      <c r="Q14" s="78"/>
-      <c r="R14" s="78"/>
-      <c r="S14" s="78"/>
-      <c r="T14" s="78"/>
-      <c r="U14" s="78"/>
-      <c r="V14" s="78"/>
-      <c r="W14" s="79"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
+      <c r="L14" s="86"/>
+      <c r="M14" s="86"/>
+      <c r="N14" s="86"/>
+      <c r="O14" s="86"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="86"/>
+      <c r="R14" s="86"/>
+      <c r="S14" s="86"/>
+      <c r="T14" s="86"/>
+      <c r="U14" s="86"/>
+      <c r="V14" s="86"/>
+      <c r="W14" s="90"/>
     </row>
     <row r="15" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="122"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="69" t="s">
+      <c r="B15" s="93"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="77"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="77"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="87"/>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="40"/>
-      <c r="K15" s="69" t="s">
+      <c r="K15" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="L15" s="77"/>
-      <c r="M15" s="122"/>
-      <c r="N15" s="77"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="93"/>
+      <c r="N15" s="87"/>
       <c r="O15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="P15" s="122"/>
-      <c r="Q15" s="77"/>
+      <c r="P15" s="93"/>
+      <c r="Q15" s="87"/>
       <c r="R15" s="7" t="s">
         <v>16</v>
       </c>
@@ -3556,400 +3556,400 @@
       <c r="T15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="U15" s="72"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="79"/>
+      <c r="U15" s="99"/>
+      <c r="V15" s="86"/>
+      <c r="W15" s="90"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="78"/>
-      <c r="N16" s="78"/>
-      <c r="O16" s="78"/>
-      <c r="P16" s="78"/>
-      <c r="Q16" s="78"/>
-      <c r="R16" s="78"/>
-      <c r="S16" s="78"/>
-      <c r="T16" s="78"/>
-      <c r="U16" s="78"/>
-      <c r="V16" s="78"/>
-      <c r="W16" s="79"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="86"/>
+      <c r="M16" s="86"/>
+      <c r="N16" s="86"/>
+      <c r="O16" s="86"/>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="86"/>
+      <c r="R16" s="86"/>
+      <c r="S16" s="86"/>
+      <c r="T16" s="86"/>
+      <c r="U16" s="86"/>
+      <c r="V16" s="86"/>
+      <c r="W16" s="90"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="92" t="s">
+      <c r="A17" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="77"/>
-      <c r="C17" s="119" t="s">
+      <c r="B17" s="87"/>
+      <c r="C17" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="81"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="119" t="s">
+      <c r="D17" s="97"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="81"/>
-      <c r="H17" s="82"/>
-      <c r="I17" s="71" t="s">
+      <c r="G17" s="97"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="77"/>
-      <c r="M17" s="119" t="s">
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="87"/>
+      <c r="M17" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="N17" s="82"/>
-      <c r="O17" s="119" t="s">
+      <c r="N17" s="95"/>
+      <c r="O17" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="P17" s="82"/>
-      <c r="Q17" s="71" t="s">
+      <c r="P17" s="95"/>
+      <c r="Q17" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="R17" s="77"/>
-      <c r="S17" s="119" t="s">
+      <c r="R17" s="87"/>
+      <c r="S17" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="T17" s="82"/>
-      <c r="U17" s="119" t="s">
+      <c r="T17" s="95"/>
+      <c r="U17" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="V17" s="81"/>
-      <c r="W17" s="120"/>
+      <c r="V17" s="97"/>
+      <c r="W17" s="98"/>
     </row>
     <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83" t="s">
+      <c r="A18" s="134" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="77"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="69" t="s">
+      <c r="B18" s="87"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="77"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="77"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="77"/>
-      <c r="Q18" s="69" t="s">
+      <c r="J18" s="86"/>
+      <c r="K18" s="86"/>
+      <c r="L18" s="87"/>
+      <c r="M18" s="99"/>
+      <c r="N18" s="87"/>
+      <c r="O18" s="99"/>
+      <c r="P18" s="87"/>
+      <c r="Q18" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="R18" s="77"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="77"/>
-      <c r="U18" s="72"/>
-      <c r="V18" s="78"/>
-      <c r="W18" s="79"/>
+      <c r="R18" s="87"/>
+      <c r="S18" s="99"/>
+      <c r="T18" s="87"/>
+      <c r="U18" s="99"/>
+      <c r="V18" s="86"/>
+      <c r="W18" s="90"/>
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="65" t="s">
+      <c r="A19" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="77"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="69" t="s">
+      <c r="B19" s="87"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="86"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="77"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="77"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="77"/>
-      <c r="Q19" s="69" t="s">
+      <c r="J19" s="86"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="99"/>
+      <c r="N19" s="87"/>
+      <c r="O19" s="99"/>
+      <c r="P19" s="87"/>
+      <c r="Q19" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="R19" s="77"/>
-      <c r="S19" s="72"/>
-      <c r="T19" s="77"/>
-      <c r="U19" s="72"/>
-      <c r="V19" s="78"/>
-      <c r="W19" s="79"/>
+      <c r="R19" s="87"/>
+      <c r="S19" s="99"/>
+      <c r="T19" s="87"/>
+      <c r="U19" s="99"/>
+      <c r="V19" s="86"/>
+      <c r="W19" s="90"/>
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="65" t="s">
+      <c r="A20" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="77"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="80" t="s">
+      <c r="B20" s="87"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="135" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="82"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="77"/>
-      <c r="O20" s="72"/>
-      <c r="P20" s="77"/>
-      <c r="Q20" s="69" t="s">
+      <c r="J20" s="97"/>
+      <c r="K20" s="97"/>
+      <c r="L20" s="95"/>
+      <c r="M20" s="99"/>
+      <c r="N20" s="87"/>
+      <c r="O20" s="99"/>
+      <c r="P20" s="87"/>
+      <c r="Q20" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="R20" s="77"/>
-      <c r="S20" s="72"/>
-      <c r="T20" s="77"/>
-      <c r="U20" s="72"/>
-      <c r="V20" s="78"/>
-      <c r="W20" s="79"/>
+      <c r="R20" s="87"/>
+      <c r="S20" s="99"/>
+      <c r="T20" s="87"/>
+      <c r="U20" s="99"/>
+      <c r="V20" s="86"/>
+      <c r="W20" s="90"/>
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="110"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="69" t="s">
+      <c r="B21" s="101"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="78"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="77"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="77"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="77"/>
-      <c r="Q21" s="69" t="s">
+      <c r="J21" s="86"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="87"/>
+      <c r="M21" s="99"/>
+      <c r="N21" s="87"/>
+      <c r="O21" s="99"/>
+      <c r="P21" s="87"/>
+      <c r="Q21" s="89" t="s">
         <v>32</v>
       </c>
-      <c r="R21" s="77"/>
-      <c r="S21" s="72"/>
-      <c r="T21" s="78"/>
-      <c r="U21" s="78"/>
-      <c r="V21" s="78"/>
-      <c r="W21" s="79"/>
+      <c r="R21" s="87"/>
+      <c r="S21" s="99"/>
+      <c r="T21" s="86"/>
+      <c r="U21" s="86"/>
+      <c r="V21" s="86"/>
+      <c r="W21" s="90"/>
     </row>
     <row r="22" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="115" t="s">
+      <c r="A22" s="107" t="s">
         <v>142</v>
       </c>
-      <c r="B22" s="115"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="117"/>
-      <c r="J22" s="117"/>
-      <c r="K22" s="117"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="117"/>
-      <c r="N22" s="117"/>
-      <c r="O22" s="117"/>
-      <c r="P22" s="117"/>
-      <c r="Q22" s="117"/>
-      <c r="R22" s="117"/>
-      <c r="S22" s="117"/>
-      <c r="T22" s="117"/>
-      <c r="U22" s="117"/>
-      <c r="V22" s="117"/>
-      <c r="W22" s="118"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="108"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="108"/>
+      <c r="G22" s="108"/>
+      <c r="H22" s="108"/>
+      <c r="I22" s="109"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="109"/>
+      <c r="L22" s="109"/>
+      <c r="M22" s="109"/>
+      <c r="N22" s="109"/>
+      <c r="O22" s="109"/>
+      <c r="P22" s="109"/>
+      <c r="Q22" s="109"/>
+      <c r="R22" s="109"/>
+      <c r="S22" s="109"/>
+      <c r="T22" s="109"/>
+      <c r="U22" s="109"/>
+      <c r="V22" s="109"/>
+      <c r="W22" s="110"/>
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="102" t="s">
+      <c r="A23" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="103"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="103"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
-      <c r="N23" s="78"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="78"/>
-      <c r="R23" s="78"/>
-      <c r="S23" s="78"/>
-      <c r="T23" s="78"/>
-      <c r="U23" s="78"/>
-      <c r="V23" s="78"/>
-      <c r="W23" s="79"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="113"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="86"/>
+      <c r="M23" s="86"/>
+      <c r="N23" s="86"/>
+      <c r="O23" s="86"/>
+      <c r="P23" s="86"/>
+      <c r="Q23" s="86"/>
+      <c r="R23" s="86"/>
+      <c r="S23" s="86"/>
+      <c r="T23" s="86"/>
+      <c r="U23" s="86"/>
+      <c r="V23" s="86"/>
+      <c r="W23" s="90"/>
     </row>
     <row r="24" spans="1:23" s="35" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="65" t="s">
+      <c r="A24" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="77"/>
-      <c r="C24" s="104"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="89" t="s">
+      <c r="B24" s="87"/>
+      <c r="C24" s="114"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="115" t="s">
         <v>141</v>
       </c>
-      <c r="F24" s="78"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="77"/>
-      <c r="L24" s="112" t="s">
+      <c r="F24" s="86"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="104" t="s">
         <v>92</v>
       </c>
-      <c r="M24" s="113"/>
-      <c r="N24" s="106"/>
-      <c r="O24" s="107"/>
-      <c r="P24" s="108"/>
-      <c r="Q24" s="114" t="s">
+      <c r="M24" s="105"/>
+      <c r="N24" s="117"/>
+      <c r="O24" s="118"/>
+      <c r="P24" s="119"/>
+      <c r="Q24" s="106" t="s">
         <v>93</v>
       </c>
-      <c r="R24" s="113"/>
-      <c r="S24" s="106"/>
-      <c r="T24" s="107"/>
-      <c r="U24" s="107"/>
-      <c r="V24" s="107"/>
-      <c r="W24" s="109"/>
+      <c r="R24" s="105"/>
+      <c r="S24" s="117"/>
+      <c r="T24" s="118"/>
+      <c r="U24" s="118"/>
+      <c r="V24" s="118"/>
+      <c r="W24" s="120"/>
     </row>
     <row r="25" spans="1:23" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="92"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="78"/>
-      <c r="K25" s="78"/>
-      <c r="L25" s="78"/>
-      <c r="M25" s="78"/>
-      <c r="N25" s="78"/>
-      <c r="O25" s="78"/>
-      <c r="P25" s="78"/>
-      <c r="Q25" s="78"/>
-      <c r="R25" s="78"/>
-      <c r="S25" s="78"/>
-      <c r="T25" s="78"/>
-      <c r="U25" s="78"/>
-      <c r="V25" s="78"/>
-      <c r="W25" s="79"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="86"/>
+      <c r="O25" s="86"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="86"/>
+      <c r="R25" s="86"/>
+      <c r="S25" s="86"/>
+      <c r="T25" s="86"/>
+      <c r="U25" s="86"/>
+      <c r="V25" s="86"/>
+      <c r="W25" s="90"/>
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="65" t="s">
+      <c r="A26" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="78"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="78"/>
-      <c r="M26" s="78"/>
-      <c r="N26" s="78"/>
-      <c r="O26" s="78"/>
-      <c r="P26" s="78"/>
-      <c r="Q26" s="78"/>
-      <c r="R26" s="78"/>
-      <c r="S26" s="78"/>
-      <c r="T26" s="78"/>
-      <c r="U26" s="78"/>
-      <c r="V26" s="78"/>
-      <c r="W26" s="79"/>
+      <c r="B26" s="86"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
+      <c r="L26" s="86"/>
+      <c r="M26" s="86"/>
+      <c r="N26" s="86"/>
+      <c r="O26" s="86"/>
+      <c r="P26" s="86"/>
+      <c r="Q26" s="86"/>
+      <c r="R26" s="86"/>
+      <c r="S26" s="86"/>
+      <c r="T26" s="86"/>
+      <c r="U26" s="86"/>
+      <c r="V26" s="86"/>
+      <c r="W26" s="90"/>
     </row>
     <row r="27" spans="1:23" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="92"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="78"/>
-      <c r="M27" s="78"/>
-      <c r="N27" s="78"/>
-      <c r="O27" s="78"/>
-      <c r="P27" s="78"/>
-      <c r="Q27" s="78"/>
-      <c r="R27" s="78"/>
-      <c r="S27" s="78"/>
-      <c r="T27" s="78"/>
-      <c r="U27" s="78"/>
-      <c r="V27" s="78"/>
-      <c r="W27" s="79"/>
+      <c r="A27" s="91"/>
+      <c r="B27" s="86"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="86"/>
+      <c r="G27" s="86"/>
+      <c r="H27" s="86"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="86"/>
+      <c r="K27" s="86"/>
+      <c r="L27" s="86"/>
+      <c r="M27" s="86"/>
+      <c r="N27" s="86"/>
+      <c r="O27" s="86"/>
+      <c r="P27" s="86"/>
+      <c r="Q27" s="86"/>
+      <c r="R27" s="86"/>
+      <c r="S27" s="86"/>
+      <c r="T27" s="86"/>
+      <c r="U27" s="86"/>
+      <c r="V27" s="86"/>
+      <c r="W27" s="90"/>
     </row>
     <row r="28" spans="1:23" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="65" t="s">
+      <c r="A28" s="92" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="66"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="66"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="66"/>
-      <c r="U28" s="66"/>
-      <c r="V28" s="66"/>
-      <c r="W28" s="67"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="136"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="136"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="136"/>
+      <c r="K28" s="136"/>
+      <c r="L28" s="136"/>
+      <c r="M28" s="136"/>
+      <c r="N28" s="136"/>
+      <c r="O28" s="136"/>
+      <c r="P28" s="136"/>
+      <c r="Q28" s="136"/>
+      <c r="R28" s="136"/>
+      <c r="S28" s="136"/>
+      <c r="T28" s="136"/>
+      <c r="U28" s="136"/>
+      <c r="V28" s="136"/>
+      <c r="W28" s="137"/>
     </row>
     <row r="29" spans="1:23" s="8" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="65" t="s">
+      <c r="A29" s="92" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="68"/>
+      <c r="B29" s="138"/>
       <c r="C29" s="6" t="s">
         <v>118</v>
       </c>
@@ -3962,10 +3962,10 @@
         <v>120</v>
       </c>
       <c r="H29" s="42"/>
-      <c r="I29" s="69" t="s">
+      <c r="I29" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="J29" s="68"/>
+      <c r="J29" s="138"/>
       <c r="K29" s="6" t="s">
         <v>121</v>
       </c>
@@ -3974,10 +3974,10 @@
         <v>122</v>
       </c>
       <c r="N29" s="42"/>
-      <c r="O29" s="69" t="s">
+      <c r="O29" s="89" t="s">
         <v>123</v>
       </c>
-      <c r="P29" s="68"/>
+      <c r="P29" s="138"/>
       <c r="R29" s="6" t="s">
         <v>37</v>
       </c>
@@ -3985,15 +3985,15 @@
       <c r="T29" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="U29" s="72"/>
-      <c r="V29" s="66"/>
-      <c r="W29" s="67"/>
+      <c r="U29" s="99"/>
+      <c r="V29" s="136"/>
+      <c r="W29" s="137"/>
     </row>
     <row r="30" spans="1:23" s="8" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="65" t="s">
+      <c r="A30" s="92" t="s">
         <v>124</v>
       </c>
-      <c r="B30" s="68"/>
+      <c r="B30" s="138"/>
       <c r="C30" s="6" t="s">
         <v>94</v>
       </c>
@@ -4006,10 +4006,10 @@
         <v>126</v>
       </c>
       <c r="H30" s="42"/>
-      <c r="I30" s="69" t="s">
+      <c r="I30" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="J30" s="68"/>
+      <c r="J30" s="138"/>
       <c r="K30" s="6" t="s">
         <v>121</v>
       </c>
@@ -4018,10 +4018,10 @@
         <v>122</v>
       </c>
       <c r="N30" s="42"/>
-      <c r="O30" s="69" t="s">
+      <c r="O30" s="89" t="s">
         <v>123</v>
       </c>
-      <c r="P30" s="68"/>
+      <c r="P30" s="138"/>
       <c r="Q30" s="42"/>
       <c r="R30" s="6" t="s">
         <v>37</v>
@@ -4030,69 +4030,69 @@
       <c r="T30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="U30" s="72"/>
-      <c r="V30" s="66"/>
-      <c r="W30" s="67"/>
+      <c r="U30" s="99"/>
+      <c r="V30" s="136"/>
+      <c r="W30" s="137"/>
     </row>
     <row r="31" spans="1:23" s="8" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="92" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="68"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="66"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="75"/>
-      <c r="M31" s="75"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="75"/>
-      <c r="P31" s="75"/>
-      <c r="Q31" s="75"/>
-      <c r="R31" s="75"/>
-      <c r="S31" s="75"/>
-      <c r="T31" s="75"/>
-      <c r="U31" s="75"/>
-      <c r="V31" s="75"/>
-      <c r="W31" s="76"/>
+      <c r="B31" s="138"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="136"/>
+      <c r="E31" s="136"/>
+      <c r="F31" s="136"/>
+      <c r="G31" s="136"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="140"/>
+      <c r="J31" s="141"/>
+      <c r="K31" s="141"/>
+      <c r="L31" s="141"/>
+      <c r="M31" s="141"/>
+      <c r="N31" s="141"/>
+      <c r="O31" s="141"/>
+      <c r="P31" s="141"/>
+      <c r="Q31" s="141"/>
+      <c r="R31" s="141"/>
+      <c r="S31" s="141"/>
+      <c r="T31" s="141"/>
+      <c r="U31" s="141"/>
+      <c r="V31" s="141"/>
+      <c r="W31" s="142"/>
     </row>
     <row r="32" spans="1:23" s="8" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="65" t="s">
+      <c r="A32" s="92" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="66"/>
-      <c r="C32" s="66"/>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="66"/>
-      <c r="M32" s="66"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="66"/>
-      <c r="P32" s="66"/>
-      <c r="Q32" s="66"/>
-      <c r="R32" s="66"/>
-      <c r="S32" s="66"/>
-      <c r="T32" s="66"/>
-      <c r="U32" s="66"/>
-      <c r="V32" s="66"/>
-      <c r="W32" s="67"/>
+      <c r="B32" s="136"/>
+      <c r="C32" s="136"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="136"/>
+      <c r="F32" s="136"/>
+      <c r="G32" s="136"/>
+      <c r="H32" s="136"/>
+      <c r="I32" s="136"/>
+      <c r="J32" s="136"/>
+      <c r="K32" s="136"/>
+      <c r="L32" s="136"/>
+      <c r="M32" s="136"/>
+      <c r="N32" s="136"/>
+      <c r="O32" s="136"/>
+      <c r="P32" s="136"/>
+      <c r="Q32" s="136"/>
+      <c r="R32" s="136"/>
+      <c r="S32" s="136"/>
+      <c r="T32" s="136"/>
+      <c r="U32" s="136"/>
+      <c r="V32" s="136"/>
+      <c r="W32" s="137"/>
     </row>
     <row r="33" spans="1:23" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="65" t="s">
+      <c r="A33" s="92" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="68"/>
+      <c r="B33" s="138"/>
       <c r="C33" s="6" t="s">
         <v>118</v>
       </c>
@@ -4104,29 +4104,29 @@
       <c r="G33" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="I33" s="69" t="s">
+      <c r="I33" s="89" t="s">
         <v>130</v>
       </c>
-      <c r="J33" s="66"/>
-      <c r="K33" s="66"/>
-      <c r="L33" s="68"/>
-      <c r="M33" s="70"/>
-      <c r="N33" s="66"/>
-      <c r="O33" s="66"/>
-      <c r="P33" s="66"/>
-      <c r="Q33" s="66"/>
-      <c r="R33" s="66"/>
-      <c r="S33" s="66"/>
-      <c r="T33" s="66"/>
-      <c r="U33" s="66"/>
-      <c r="V33" s="66"/>
-      <c r="W33" s="67"/>
+      <c r="J33" s="136"/>
+      <c r="K33" s="136"/>
+      <c r="L33" s="138"/>
+      <c r="M33" s="143"/>
+      <c r="N33" s="136"/>
+      <c r="O33" s="136"/>
+      <c r="P33" s="136"/>
+      <c r="Q33" s="136"/>
+      <c r="R33" s="136"/>
+      <c r="S33" s="136"/>
+      <c r="T33" s="136"/>
+      <c r="U33" s="136"/>
+      <c r="V33" s="136"/>
+      <c r="W33" s="137"/>
     </row>
     <row r="34" spans="1:23" s="8" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="65" t="s">
+      <c r="A34" s="92" t="s">
         <v>131</v>
       </c>
-      <c r="B34" s="68"/>
+      <c r="B34" s="138"/>
       <c r="C34" s="6" t="s">
         <v>94</v>
       </c>
@@ -4139,245 +4139,245 @@
         <v>126</v>
       </c>
       <c r="H34" s="42"/>
-      <c r="I34" s="69" t="s">
+      <c r="I34" s="89" t="s">
         <v>132</v>
       </c>
-      <c r="J34" s="66"/>
-      <c r="K34" s="66"/>
-      <c r="L34" s="68"/>
-      <c r="M34" s="71" t="s">
+      <c r="J34" s="136"/>
+      <c r="K34" s="136"/>
+      <c r="L34" s="138"/>
+      <c r="M34" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="N34" s="66"/>
-      <c r="O34" s="68"/>
-      <c r="P34" s="72"/>
-      <c r="Q34" s="68"/>
-      <c r="R34" s="71" t="s">
+      <c r="N34" s="136"/>
+      <c r="O34" s="138"/>
+      <c r="P34" s="99"/>
+      <c r="Q34" s="138"/>
+      <c r="R34" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="S34" s="66"/>
-      <c r="T34" s="68"/>
-      <c r="U34" s="72"/>
-      <c r="V34" s="66"/>
-      <c r="W34" s="67"/>
+      <c r="S34" s="136"/>
+      <c r="T34" s="138"/>
+      <c r="U34" s="99"/>
+      <c r="V34" s="136"/>
+      <c r="W34" s="137"/>
     </row>
     <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
-      <c r="I35" s="78"/>
-      <c r="J35" s="78"/>
-      <c r="K35" s="78"/>
-      <c r="L35" s="78"/>
-      <c r="M35" s="78"/>
-      <c r="N35" s="78"/>
-      <c r="O35" s="78"/>
-      <c r="P35" s="78"/>
-      <c r="Q35" s="78"/>
-      <c r="R35" s="78"/>
-      <c r="S35" s="78"/>
-      <c r="T35" s="78"/>
-      <c r="U35" s="78"/>
-      <c r="V35" s="78"/>
-      <c r="W35" s="79"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="86"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="86"/>
+      <c r="F35" s="86"/>
+      <c r="G35" s="86"/>
+      <c r="H35" s="86"/>
+      <c r="I35" s="86"/>
+      <c r="J35" s="86"/>
+      <c r="K35" s="86"/>
+      <c r="L35" s="86"/>
+      <c r="M35" s="86"/>
+      <c r="N35" s="86"/>
+      <c r="O35" s="86"/>
+      <c r="P35" s="86"/>
+      <c r="Q35" s="86"/>
+      <c r="R35" s="86"/>
+      <c r="S35" s="86"/>
+      <c r="T35" s="86"/>
+      <c r="U35" s="86"/>
+      <c r="V35" s="86"/>
+      <c r="W35" s="90"/>
     </row>
     <row r="36" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="65" t="s">
+      <c r="A36" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="78"/>
-      <c r="C36" s="78"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="100" t="s">
+      <c r="B36" s="86"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="87"/>
+      <c r="E36" s="99"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="133" t="s">
         <v>95</v>
       </c>
-      <c r="H36" s="81"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="81"/>
-      <c r="K36" s="81"/>
-      <c r="L36" s="82"/>
-      <c r="M36" s="88"/>
-      <c r="N36" s="77"/>
-      <c r="O36" s="89" t="s">
+      <c r="H36" s="97"/>
+      <c r="I36" s="97"/>
+      <c r="J36" s="97"/>
+      <c r="K36" s="97"/>
+      <c r="L36" s="95"/>
+      <c r="M36" s="125"/>
+      <c r="N36" s="87"/>
+      <c r="O36" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="P36" s="78"/>
-      <c r="Q36" s="78"/>
-      <c r="R36" s="77"/>
-      <c r="S36" s="101"/>
-      <c r="T36" s="78"/>
-      <c r="U36" s="78"/>
-      <c r="V36" s="78"/>
-      <c r="W36" s="79"/>
+      <c r="P36" s="86"/>
+      <c r="Q36" s="86"/>
+      <c r="R36" s="87"/>
+      <c r="S36" s="111"/>
+      <c r="T36" s="86"/>
+      <c r="U36" s="86"/>
+      <c r="V36" s="86"/>
+      <c r="W36" s="90"/>
     </row>
     <row r="37" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="90" t="s">
+      <c r="A37" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="91"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="78"/>
-      <c r="E37" s="78"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
-      <c r="M37" s="78"/>
-      <c r="N37" s="78"/>
-      <c r="O37" s="78"/>
-      <c r="P37" s="78"/>
-      <c r="Q37" s="78"/>
-      <c r="R37" s="78"/>
-      <c r="S37" s="78"/>
-      <c r="T37" s="78"/>
-      <c r="U37" s="78"/>
-      <c r="V37" s="78"/>
-      <c r="W37" s="79"/>
+      <c r="B37" s="103"/>
+      <c r="C37" s="125"/>
+      <c r="D37" s="86"/>
+      <c r="E37" s="86"/>
+      <c r="F37" s="86"/>
+      <c r="G37" s="86"/>
+      <c r="H37" s="86"/>
+      <c r="I37" s="86"/>
+      <c r="J37" s="86"/>
+      <c r="K37" s="86"/>
+      <c r="L37" s="86"/>
+      <c r="M37" s="86"/>
+      <c r="N37" s="86"/>
+      <c r="O37" s="86"/>
+      <c r="P37" s="86"/>
+      <c r="Q37" s="86"/>
+      <c r="R37" s="86"/>
+      <c r="S37" s="86"/>
+      <c r="T37" s="86"/>
+      <c r="U37" s="86"/>
+      <c r="V37" s="86"/>
+      <c r="W37" s="90"/>
     </row>
     <row r="38" spans="1:23" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="92"/>
-      <c r="B38" s="78"/>
-      <c r="C38" s="78"/>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="78"/>
-      <c r="H38" s="78"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="78"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="78"/>
-      <c r="M38" s="78"/>
-      <c r="N38" s="78"/>
-      <c r="O38" s="78"/>
-      <c r="P38" s="78"/>
-      <c r="Q38" s="78"/>
-      <c r="R38" s="78"/>
-      <c r="S38" s="78"/>
-      <c r="T38" s="78"/>
-      <c r="U38" s="78"/>
-      <c r="V38" s="78"/>
-      <c r="W38" s="79"/>
+      <c r="A38" s="91"/>
+      <c r="B38" s="86"/>
+      <c r="C38" s="86"/>
+      <c r="D38" s="86"/>
+      <c r="E38" s="86"/>
+      <c r="F38" s="86"/>
+      <c r="G38" s="86"/>
+      <c r="H38" s="86"/>
+      <c r="I38" s="86"/>
+      <c r="J38" s="86"/>
+      <c r="K38" s="86"/>
+      <c r="L38" s="86"/>
+      <c r="M38" s="86"/>
+      <c r="N38" s="86"/>
+      <c r="O38" s="86"/>
+      <c r="P38" s="86"/>
+      <c r="Q38" s="86"/>
+      <c r="R38" s="86"/>
+      <c r="S38" s="86"/>
+      <c r="T38" s="86"/>
+      <c r="U38" s="86"/>
+      <c r="V38" s="86"/>
+      <c r="W38" s="90"/>
     </row>
     <row r="39" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="93" t="s">
+      <c r="A39" s="126" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="94"/>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
-      <c r="F39" s="94"/>
-      <c r="G39" s="94"/>
-      <c r="H39" s="94"/>
-      <c r="I39" s="94"/>
-      <c r="J39" s="94"/>
-      <c r="K39" s="94"/>
-      <c r="L39" s="94"/>
-      <c r="M39" s="94"/>
-      <c r="N39" s="94"/>
-      <c r="O39" s="94"/>
-      <c r="P39" s="94"/>
-      <c r="Q39" s="94"/>
-      <c r="R39" s="94"/>
-      <c r="S39" s="94"/>
-      <c r="T39" s="94"/>
-      <c r="U39" s="94"/>
-      <c r="V39" s="94"/>
-      <c r="W39" s="95"/>
+      <c r="B39" s="127"/>
+      <c r="C39" s="127"/>
+      <c r="D39" s="127"/>
+      <c r="E39" s="127"/>
+      <c r="F39" s="127"/>
+      <c r="G39" s="127"/>
+      <c r="H39" s="127"/>
+      <c r="I39" s="127"/>
+      <c r="J39" s="127"/>
+      <c r="K39" s="127"/>
+      <c r="L39" s="127"/>
+      <c r="M39" s="127"/>
+      <c r="N39" s="127"/>
+      <c r="O39" s="127"/>
+      <c r="P39" s="127"/>
+      <c r="Q39" s="127"/>
+      <c r="R39" s="127"/>
+      <c r="S39" s="127"/>
+      <c r="T39" s="127"/>
+      <c r="U39" s="127"/>
+      <c r="V39" s="127"/>
+      <c r="W39" s="128"/>
     </row>
     <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="97" t="s">
+      <c r="A40" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="77"/>
-      <c r="C40" s="96"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="78"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="78"/>
-      <c r="L40" s="78"/>
-      <c r="M40" s="78"/>
-      <c r="N40" s="78"/>
-      <c r="O40" s="78"/>
-      <c r="P40" s="78"/>
-      <c r="Q40" s="78"/>
-      <c r="R40" s="78"/>
-      <c r="S40" s="78"/>
-      <c r="T40" s="78"/>
-      <c r="U40" s="78"/>
-      <c r="V40" s="78"/>
-      <c r="W40" s="79"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="129"/>
+      <c r="D40" s="86"/>
+      <c r="E40" s="86"/>
+      <c r="F40" s="86"/>
+      <c r="G40" s="86"/>
+      <c r="H40" s="86"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="86"/>
+      <c r="K40" s="86"/>
+      <c r="L40" s="86"/>
+      <c r="M40" s="86"/>
+      <c r="N40" s="86"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="86"/>
+      <c r="Q40" s="86"/>
+      <c r="R40" s="86"/>
+      <c r="S40" s="86"/>
+      <c r="T40" s="86"/>
+      <c r="U40" s="86"/>
+      <c r="V40" s="86"/>
+      <c r="W40" s="90"/>
     </row>
     <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="97" t="s">
+      <c r="A41" s="130" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="77"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="78"/>
-      <c r="E41" s="78"/>
-      <c r="F41" s="78"/>
-      <c r="G41" s="78"/>
-      <c r="H41" s="78"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="78"/>
-      <c r="K41" s="78"/>
-      <c r="L41" s="78"/>
-      <c r="M41" s="78"/>
-      <c r="N41" s="78"/>
-      <c r="O41" s="78"/>
-      <c r="P41" s="78"/>
-      <c r="Q41" s="78"/>
-      <c r="R41" s="78"/>
-      <c r="S41" s="78"/>
-      <c r="T41" s="78"/>
-      <c r="U41" s="78"/>
-      <c r="V41" s="78"/>
-      <c r="W41" s="79"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="121"/>
+      <c r="D41" s="86"/>
+      <c r="E41" s="86"/>
+      <c r="F41" s="86"/>
+      <c r="G41" s="86"/>
+      <c r="H41" s="86"/>
+      <c r="I41" s="86"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="86"/>
+      <c r="L41" s="86"/>
+      <c r="M41" s="86"/>
+      <c r="N41" s="86"/>
+      <c r="O41" s="86"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="86"/>
+      <c r="S41" s="86"/>
+      <c r="T41" s="86"/>
+      <c r="U41" s="86"/>
+      <c r="V41" s="86"/>
+      <c r="W41" s="90"/>
     </row>
     <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="98" t="s">
+      <c r="A42" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="99"/>
-      <c r="C42" s="85"/>
-      <c r="D42" s="86"/>
-      <c r="E42" s="86"/>
-      <c r="F42" s="86"/>
-      <c r="G42" s="86"/>
-      <c r="H42" s="86"/>
-      <c r="I42" s="86"/>
-      <c r="J42" s="86"/>
-      <c r="K42" s="86"/>
-      <c r="L42" s="86"/>
-      <c r="M42" s="86"/>
-      <c r="N42" s="86"/>
-      <c r="O42" s="86"/>
-      <c r="P42" s="86"/>
-      <c r="Q42" s="86"/>
-      <c r="R42" s="86"/>
-      <c r="S42" s="86"/>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
-      <c r="V42" s="86"/>
-      <c r="W42" s="87"/>
+      <c r="B42" s="132"/>
+      <c r="C42" s="122"/>
+      <c r="D42" s="123"/>
+      <c r="E42" s="123"/>
+      <c r="F42" s="123"/>
+      <c r="G42" s="123"/>
+      <c r="H42" s="123"/>
+      <c r="I42" s="123"/>
+      <c r="J42" s="123"/>
+      <c r="K42" s="123"/>
+      <c r="L42" s="123"/>
+      <c r="M42" s="123"/>
+      <c r="N42" s="123"/>
+      <c r="O42" s="123"/>
+      <c r="P42" s="123"/>
+      <c r="Q42" s="123"/>
+      <c r="R42" s="123"/>
+      <c r="S42" s="123"/>
+      <c r="T42" s="123"/>
+      <c r="U42" s="123"/>
+      <c r="V42" s="123"/>
+      <c r="W42" s="124"/>
     </row>
     <row r="43" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
@@ -28431,15 +28431,106 @@
     </row>
   </sheetData>
   <mergeCells count="123">
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:W10"/>
-    <mergeCell ref="A1:E8"/>
-    <mergeCell ref="F1:R8"/>
-    <mergeCell ref="S1:W8"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="M9:Q9"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A32:W32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="M33:W33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="U34:W34"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="U18:W18"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="C41:W41"/>
+    <mergeCell ref="C42:W42"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="O36:R36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:W37"/>
+    <mergeCell ref="A38:W38"/>
+    <mergeCell ref="A39:W39"/>
+    <mergeCell ref="C40:W40"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="G36:L36"/>
+    <mergeCell ref="A27:W27"/>
+    <mergeCell ref="A35:W35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="S36:W36"/>
+    <mergeCell ref="A23:W23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="H24:K24"/>
+    <mergeCell ref="A25:W25"/>
+    <mergeCell ref="A26:W26"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="S24:W24"/>
+    <mergeCell ref="A28:W28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="U29:W29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="U30:W30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="I31:W31"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="S21:W21"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="I22:W22"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="U17:W17"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="A16:W16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="M17:N17"/>
     <mergeCell ref="B11:J11"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="M11:W11"/>
@@ -28454,106 +28545,15 @@
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="M15:N15"/>
     <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="U17:W17"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="A16:W16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="S21:W21"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="I22:W22"/>
-    <mergeCell ref="A27:W27"/>
-    <mergeCell ref="A35:W35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="S36:W36"/>
-    <mergeCell ref="A23:W23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="A25:W25"/>
-    <mergeCell ref="A26:W26"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="S24:W24"/>
-    <mergeCell ref="C41:W41"/>
-    <mergeCell ref="C42:W42"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="O36:R36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:W37"/>
-    <mergeCell ref="A38:W38"/>
-    <mergeCell ref="A39:W39"/>
-    <mergeCell ref="C40:W40"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G36:L36"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="U18:W18"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="U19:W19"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="U20:W20"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="A28:W28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="U29:W29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="U30:W30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="I31:W31"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A32:W32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="M33:W33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="U34:W34"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:W10"/>
+    <mergeCell ref="A1:E8"/>
+    <mergeCell ref="F1:R8"/>
+    <mergeCell ref="S1:W8"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="M9:Q9"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="B10:J10"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="M15:N15" xr:uid="{F620CAB2-40BA-4C09-AC23-42082F68B8A3}"/>
@@ -28580,19 +28580,19 @@
   <sheetData>
     <row r="1" spans="1:4" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9"/>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="144" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="128"/>
+      <c r="C1" s="71"/>
       <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="155"/>
-      <c r="C2" s="155"/>
-      <c r="D2" s="156"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="147"/>
     </row>
     <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
@@ -28609,114 +28609,114 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="147"/>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="150"/>
+      <c r="A4" s="148"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="148"/>
+      <c r="D4" s="151"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="148"/>
-      <c r="B5" s="148"/>
-      <c r="C5" s="148"/>
-      <c r="D5" s="151"/>
+      <c r="A5" s="149"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="149"/>
+      <c r="D5" s="152"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="148"/>
-      <c r="B6" s="148"/>
-      <c r="C6" s="148"/>
-      <c r="D6" s="151"/>
+      <c r="A6" s="149"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="152"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="148"/>
-      <c r="B7" s="148"/>
-      <c r="C7" s="148"/>
-      <c r="D7" s="151"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="149"/>
+      <c r="C7" s="149"/>
+      <c r="D7" s="152"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="148"/>
-      <c r="B8" s="148"/>
-      <c r="C8" s="148"/>
-      <c r="D8" s="151"/>
+      <c r="A8" s="149"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="149"/>
+      <c r="D8" s="152"/>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="148"/>
-      <c r="B9" s="148"/>
-      <c r="C9" s="148"/>
-      <c r="D9" s="151"/>
+      <c r="A9" s="149"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="149"/>
+      <c r="D9" s="152"/>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="148"/>
-      <c r="B10" s="148"/>
-      <c r="C10" s="148"/>
-      <c r="D10" s="151"/>
+      <c r="A10" s="149"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="149"/>
+      <c r="D10" s="152"/>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="148"/>
-      <c r="B11" s="148"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="151"/>
+      <c r="A11" s="149"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="149"/>
+      <c r="D11" s="152"/>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="148"/>
-      <c r="B12" s="148"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="151"/>
+      <c r="A12" s="149"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="149"/>
+      <c r="D12" s="152"/>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="148"/>
-      <c r="B13" s="148"/>
-      <c r="C13" s="148"/>
-      <c r="D13" s="151"/>
+      <c r="A13" s="149"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="149"/>
+      <c r="D13" s="152"/>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="148"/>
-      <c r="B14" s="148"/>
-      <c r="C14" s="148"/>
-      <c r="D14" s="151"/>
+      <c r="A14" s="149"/>
+      <c r="B14" s="149"/>
+      <c r="C14" s="149"/>
+      <c r="D14" s="152"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="148"/>
-      <c r="B15" s="148"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="151"/>
+      <c r="A15" s="149"/>
+      <c r="B15" s="149"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="152"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="148"/>
-      <c r="B16" s="148"/>
-      <c r="C16" s="148"/>
-      <c r="D16" s="151"/>
+      <c r="A16" s="149"/>
+      <c r="B16" s="149"/>
+      <c r="C16" s="149"/>
+      <c r="D16" s="152"/>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="148"/>
-      <c r="B17" s="148"/>
-      <c r="C17" s="148"/>
-      <c r="D17" s="151"/>
+      <c r="A17" s="149"/>
+      <c r="B17" s="149"/>
+      <c r="C17" s="149"/>
+      <c r="D17" s="152"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="148"/>
-      <c r="B18" s="148"/>
-      <c r="C18" s="148"/>
-      <c r="D18" s="151"/>
+      <c r="A18" s="149"/>
+      <c r="B18" s="149"/>
+      <c r="C18" s="149"/>
+      <c r="D18" s="152"/>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="148"/>
-      <c r="B19" s="148"/>
-      <c r="C19" s="148"/>
-      <c r="D19" s="151"/>
+      <c r="A19" s="149"/>
+      <c r="B19" s="149"/>
+      <c r="C19" s="149"/>
+      <c r="D19" s="152"/>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="149"/>
-      <c r="B20" s="149"/>
-      <c r="C20" s="149"/>
-      <c r="D20" s="162"/>
+      <c r="A20" s="150"/>
+      <c r="B20" s="150"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="153"/>
     </row>
     <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="154" t="s">
+      <c r="A21" s="145" t="s">
         <v>163</v>
       </c>
-      <c r="B21" s="155"/>
-      <c r="C21" s="155"/>
-      <c r="D21" s="156"/>
+      <c r="B21" s="146"/>
+      <c r="C21" s="146"/>
+      <c r="D21" s="147"/>
     </row>
     <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
@@ -28734,106 +28734,106 @@
       <c r="E22" s="13"/>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="147"/>
-      <c r="B23" s="147"/>
-      <c r="C23" s="147"/>
-      <c r="D23" s="150"/>
+      <c r="A23" s="148"/>
+      <c r="B23" s="148"/>
+      <c r="C23" s="148"/>
+      <c r="D23" s="151"/>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="148"/>
-      <c r="B24" s="148"/>
-      <c r="C24" s="148"/>
-      <c r="D24" s="151"/>
+      <c r="A24" s="149"/>
+      <c r="B24" s="149"/>
+      <c r="C24" s="149"/>
+      <c r="D24" s="152"/>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="148"/>
-      <c r="B25" s="148"/>
-      <c r="C25" s="148"/>
-      <c r="D25" s="151"/>
+      <c r="A25" s="149"/>
+      <c r="B25" s="149"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="152"/>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="148"/>
-      <c r="B26" s="148"/>
-      <c r="C26" s="148"/>
-      <c r="D26" s="151"/>
+      <c r="A26" s="149"/>
+      <c r="B26" s="149"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="152"/>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="148"/>
-      <c r="B27" s="148"/>
-      <c r="C27" s="148"/>
-      <c r="D27" s="151"/>
+      <c r="A27" s="149"/>
+      <c r="B27" s="149"/>
+      <c r="C27" s="149"/>
+      <c r="D27" s="152"/>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="148"/>
-      <c r="B28" s="148"/>
-      <c r="C28" s="148"/>
-      <c r="D28" s="151"/>
+      <c r="A28" s="149"/>
+      <c r="B28" s="149"/>
+      <c r="C28" s="149"/>
+      <c r="D28" s="152"/>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="148"/>
-      <c r="B29" s="148"/>
-      <c r="C29" s="148"/>
-      <c r="D29" s="151"/>
+      <c r="A29" s="149"/>
+      <c r="B29" s="149"/>
+      <c r="C29" s="149"/>
+      <c r="D29" s="152"/>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="148"/>
-      <c r="B30" s="148"/>
-      <c r="C30" s="148"/>
-      <c r="D30" s="151"/>
+      <c r="A30" s="149"/>
+      <c r="B30" s="149"/>
+      <c r="C30" s="149"/>
+      <c r="D30" s="152"/>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="148"/>
-      <c r="B31" s="148"/>
-      <c r="C31" s="148"/>
-      <c r="D31" s="151"/>
+      <c r="A31" s="149"/>
+      <c r="B31" s="149"/>
+      <c r="C31" s="149"/>
+      <c r="D31" s="152"/>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="148"/>
-      <c r="B32" s="148"/>
-      <c r="C32" s="148"/>
-      <c r="D32" s="151"/>
+      <c r="A32" s="149"/>
+      <c r="B32" s="149"/>
+      <c r="C32" s="149"/>
+      <c r="D32" s="152"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="148"/>
-      <c r="B33" s="148"/>
-      <c r="C33" s="148"/>
-      <c r="D33" s="151"/>
+      <c r="A33" s="149"/>
+      <c r="B33" s="149"/>
+      <c r="C33" s="149"/>
+      <c r="D33" s="152"/>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="148"/>
-      <c r="B34" s="148"/>
-      <c r="C34" s="148"/>
-      <c r="D34" s="151"/>
+      <c r="A34" s="149"/>
+      <c r="B34" s="149"/>
+      <c r="C34" s="149"/>
+      <c r="D34" s="152"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="148"/>
-      <c r="B35" s="148"/>
-      <c r="C35" s="148"/>
-      <c r="D35" s="151"/>
+      <c r="A35" s="149"/>
+      <c r="B35" s="149"/>
+      <c r="C35" s="149"/>
+      <c r="D35" s="152"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="148"/>
-      <c r="B36" s="148"/>
-      <c r="C36" s="148"/>
-      <c r="D36" s="151"/>
+      <c r="A36" s="149"/>
+      <c r="B36" s="149"/>
+      <c r="C36" s="149"/>
+      <c r="D36" s="152"/>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="148"/>
-      <c r="B37" s="148"/>
-      <c r="C37" s="148"/>
-      <c r="D37" s="151"/>
+      <c r="A37" s="149"/>
+      <c r="B37" s="149"/>
+      <c r="C37" s="149"/>
+      <c r="D37" s="152"/>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="148"/>
-      <c r="B38" s="148"/>
-      <c r="C38" s="148"/>
-      <c r="D38" s="151"/>
+      <c r="A38" s="149"/>
+      <c r="B38" s="149"/>
+      <c r="C38" s="149"/>
+      <c r="D38" s="152"/>
     </row>
     <row r="39" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="149"/>
-      <c r="B39" s="149"/>
-      <c r="C39" s="149"/>
-      <c r="D39" s="151"/>
+      <c r="A39" s="150"/>
+      <c r="B39" s="150"/>
+      <c r="C39" s="150"/>
+      <c r="D39" s="152"/>
     </row>
     <row r="40" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
@@ -28850,84 +28850,84 @@
       </c>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="150"/>
-      <c r="B41" s="150"/>
-      <c r="C41" s="150"/>
-      <c r="D41" s="153"/>
+      <c r="A41" s="151"/>
+      <c r="B41" s="151"/>
+      <c r="C41" s="151"/>
+      <c r="D41" s="163"/>
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="151"/>
-      <c r="B42" s="151"/>
-      <c r="C42" s="151"/>
-      <c r="D42" s="151"/>
+      <c r="A42" s="152"/>
+      <c r="B42" s="152"/>
+      <c r="C42" s="152"/>
+      <c r="D42" s="152"/>
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="151"/>
-      <c r="B43" s="151"/>
-      <c r="C43" s="151"/>
-      <c r="D43" s="151"/>
+      <c r="A43" s="152"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="151"/>
-      <c r="B44" s="151"/>
-      <c r="C44" s="151"/>
-      <c r="D44" s="151"/>
+      <c r="A44" s="152"/>
+      <c r="B44" s="152"/>
+      <c r="C44" s="152"/>
+      <c r="D44" s="152"/>
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="151"/>
-      <c r="B45" s="151"/>
-      <c r="C45" s="151"/>
-      <c r="D45" s="151"/>
+      <c r="A45" s="152"/>
+      <c r="B45" s="152"/>
+      <c r="C45" s="152"/>
+      <c r="D45" s="152"/>
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="151"/>
-      <c r="B46" s="151"/>
-      <c r="C46" s="151"/>
-      <c r="D46" s="151"/>
+      <c r="A46" s="152"/>
+      <c r="B46" s="152"/>
+      <c r="C46" s="152"/>
+      <c r="D46" s="152"/>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="151"/>
-      <c r="B47" s="151"/>
-      <c r="C47" s="151"/>
-      <c r="D47" s="151"/>
+      <c r="A47" s="152"/>
+      <c r="B47" s="152"/>
+      <c r="C47" s="152"/>
+      <c r="D47" s="152"/>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="151"/>
-      <c r="B48" s="151"/>
-      <c r="C48" s="151"/>
-      <c r="D48" s="151"/>
+      <c r="A48" s="152"/>
+      <c r="B48" s="152"/>
+      <c r="C48" s="152"/>
+      <c r="D48" s="152"/>
     </row>
     <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="151"/>
-      <c r="B49" s="151"/>
-      <c r="C49" s="151"/>
-      <c r="D49" s="151"/>
+      <c r="A49" s="152"/>
+      <c r="B49" s="152"/>
+      <c r="C49" s="152"/>
+      <c r="D49" s="152"/>
       <c r="F49" s="14"/>
     </row>
     <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="151"/>
-      <c r="B50" s="151"/>
-      <c r="C50" s="151"/>
-      <c r="D50" s="151"/>
+      <c r="A50" s="152"/>
+      <c r="B50" s="152"/>
+      <c r="C50" s="152"/>
+      <c r="D50" s="152"/>
       <c r="F50" s="14"/>
     </row>
     <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="151"/>
-      <c r="B51" s="151"/>
-      <c r="C51" s="151"/>
-      <c r="D51" s="151"/>
+      <c r="A51" s="152"/>
+      <c r="B51" s="152"/>
+      <c r="C51" s="152"/>
+      <c r="D51" s="152"/>
     </row>
     <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="151"/>
-      <c r="B52" s="151"/>
-      <c r="C52" s="151"/>
-      <c r="D52" s="151"/>
+      <c r="A52" s="152"/>
+      <c r="B52" s="152"/>
+      <c r="C52" s="152"/>
+      <c r="D52" s="152"/>
     </row>
     <row r="53" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="151"/>
-      <c r="B53" s="151"/>
-      <c r="C53" s="151"/>
-      <c r="D53" s="151"/>
+      <c r="A53" s="152"/>
+      <c r="B53" s="152"/>
+      <c r="C53" s="152"/>
+      <c r="D53" s="152"/>
       <c r="F53" s="15"/>
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
@@ -28936,10 +28936,10 @@
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="151"/>
-      <c r="B54" s="151"/>
-      <c r="C54" s="151"/>
-      <c r="D54" s="151"/>
+      <c r="A54" s="152"/>
+      <c r="B54" s="152"/>
+      <c r="C54" s="152"/>
+      <c r="D54" s="152"/>
       <c r="F54" s="14"/>
       <c r="G54" s="15"/>
       <c r="H54" s="15"/>
@@ -28948,10 +28948,10 @@
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="151"/>
-      <c r="B55" s="151"/>
-      <c r="C55" s="151"/>
-      <c r="D55" s="151"/>
+      <c r="A55" s="152"/>
+      <c r="B55" s="152"/>
+      <c r="C55" s="152"/>
+      <c r="D55" s="152"/>
       <c r="F55" s="14"/>
       <c r="G55" s="15"/>
       <c r="H55" s="15"/>
@@ -28960,10 +28960,10 @@
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="151"/>
-      <c r="B56" s="151"/>
-      <c r="C56" s="151"/>
-      <c r="D56" s="151"/>
+      <c r="A56" s="152"/>
+      <c r="B56" s="152"/>
+      <c r="C56" s="152"/>
+      <c r="D56" s="152"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15"/>
       <c r="H56" s="15"/>
@@ -28972,10 +28972,10 @@
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="152"/>
-      <c r="B57" s="152"/>
-      <c r="C57" s="152"/>
-      <c r="D57" s="152"/>
+      <c r="A57" s="154"/>
+      <c r="B57" s="154"/>
+      <c r="C57" s="154"/>
+      <c r="D57" s="154"/>
       <c r="F57" s="15"/>
       <c r="G57" s="15"/>
       <c r="H57" s="15"/>
@@ -29004,10 +29004,10 @@
       <c r="K58" s="28"/>
     </row>
     <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="150"/>
-      <c r="B59" s="150"/>
-      <c r="C59" s="150"/>
-      <c r="D59" s="150"/>
+      <c r="A59" s="151"/>
+      <c r="B59" s="151"/>
+      <c r="C59" s="151"/>
+      <c r="D59" s="151"/>
       <c r="F59" s="15"/>
       <c r="G59" s="15"/>
       <c r="H59" s="15"/>
@@ -29016,10 +29016,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="151"/>
-      <c r="B60" s="151"/>
-      <c r="C60" s="151"/>
-      <c r="D60" s="151"/>
+      <c r="A60" s="152"/>
+      <c r="B60" s="152"/>
+      <c r="C60" s="152"/>
+      <c r="D60" s="152"/>
       <c r="F60" s="15"/>
       <c r="G60" s="15"/>
       <c r="H60" s="15"/>
@@ -29028,10 +29028,10 @@
       <c r="K60" s="15"/>
     </row>
     <row r="61" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="151"/>
-      <c r="B61" s="151"/>
-      <c r="C61" s="151"/>
-      <c r="D61" s="151"/>
+      <c r="A61" s="152"/>
+      <c r="B61" s="152"/>
+      <c r="C61" s="152"/>
+      <c r="D61" s="152"/>
       <c r="F61" s="15"/>
       <c r="G61" s="15"/>
       <c r="H61" s="15"/>
@@ -29040,10 +29040,10 @@
       <c r="K61" s="15"/>
     </row>
     <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="151"/>
-      <c r="B62" s="151"/>
-      <c r="C62" s="151"/>
-      <c r="D62" s="151"/>
+      <c r="A62" s="152"/>
+      <c r="B62" s="152"/>
+      <c r="C62" s="152"/>
+      <c r="D62" s="152"/>
       <c r="F62" s="15"/>
       <c r="G62" s="15"/>
       <c r="H62" s="15"/>
@@ -29052,82 +29052,82 @@
       <c r="K62" s="15"/>
     </row>
     <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="151"/>
-      <c r="B63" s="151"/>
-      <c r="C63" s="151"/>
-      <c r="D63" s="151"/>
+      <c r="A63" s="152"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
     </row>
     <row r="64" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="151"/>
-      <c r="B64" s="151"/>
-      <c r="C64" s="151"/>
-      <c r="D64" s="151"/>
+      <c r="A64" s="152"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="151"/>
-      <c r="B65" s="151"/>
-      <c r="C65" s="151"/>
-      <c r="D65" s="151"/>
+      <c r="A65" s="152"/>
+      <c r="B65" s="152"/>
+      <c r="C65" s="152"/>
+      <c r="D65" s="152"/>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="151"/>
-      <c r="B66" s="151"/>
-      <c r="C66" s="151"/>
-      <c r="D66" s="151"/>
+      <c r="A66" s="152"/>
+      <c r="B66" s="152"/>
+      <c r="C66" s="152"/>
+      <c r="D66" s="152"/>
     </row>
     <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="151"/>
-      <c r="B67" s="151"/>
-      <c r="C67" s="151"/>
-      <c r="D67" s="151"/>
+      <c r="A67" s="152"/>
+      <c r="B67" s="152"/>
+      <c r="C67" s="152"/>
+      <c r="D67" s="152"/>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="151"/>
-      <c r="B68" s="151"/>
-      <c r="C68" s="151"/>
-      <c r="D68" s="151"/>
+      <c r="A68" s="152"/>
+      <c r="B68" s="152"/>
+      <c r="C68" s="152"/>
+      <c r="D68" s="152"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="151"/>
-      <c r="B69" s="151"/>
-      <c r="C69" s="151"/>
-      <c r="D69" s="151"/>
+      <c r="A69" s="152"/>
+      <c r="B69" s="152"/>
+      <c r="C69" s="152"/>
+      <c r="D69" s="152"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="151"/>
-      <c r="B70" s="151"/>
-      <c r="C70" s="151"/>
-      <c r="D70" s="151"/>
+      <c r="A70" s="152"/>
+      <c r="B70" s="152"/>
+      <c r="C70" s="152"/>
+      <c r="D70" s="152"/>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="151"/>
-      <c r="B71" s="151"/>
-      <c r="C71" s="151"/>
-      <c r="D71" s="151"/>
+      <c r="A71" s="152"/>
+      <c r="B71" s="152"/>
+      <c r="C71" s="152"/>
+      <c r="D71" s="152"/>
     </row>
     <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="151"/>
-      <c r="B72" s="151"/>
-      <c r="C72" s="151"/>
-      <c r="D72" s="151"/>
+      <c r="A72" s="152"/>
+      <c r="B72" s="152"/>
+      <c r="C72" s="152"/>
+      <c r="D72" s="152"/>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="151"/>
-      <c r="B73" s="151"/>
-      <c r="C73" s="151"/>
-      <c r="D73" s="151"/>
+      <c r="A73" s="152"/>
+      <c r="B73" s="152"/>
+      <c r="C73" s="152"/>
+      <c r="D73" s="152"/>
     </row>
     <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="151"/>
-      <c r="B74" s="151"/>
-      <c r="C74" s="151"/>
-      <c r="D74" s="151"/>
+      <c r="A74" s="152"/>
+      <c r="B74" s="152"/>
+      <c r="C74" s="152"/>
+      <c r="D74" s="152"/>
     </row>
     <row r="75" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="152"/>
-      <c r="B75" s="152"/>
-      <c r="C75" s="152"/>
-      <c r="D75" s="152"/>
+      <c r="A75" s="154"/>
+      <c r="B75" s="154"/>
+      <c r="C75" s="154"/>
+      <c r="D75" s="154"/>
     </row>
     <row r="76" spans="1:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="62" t="s">
@@ -29144,138 +29144,138 @@
       <c r="F76" s="16"/>
     </row>
     <row r="77" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="157"/>
-      <c r="B77" s="157"/>
-      <c r="C77" s="159"/>
-      <c r="D77" s="150"/>
+      <c r="A77" s="155"/>
+      <c r="B77" s="155"/>
+      <c r="C77" s="157"/>
+      <c r="D77" s="151"/>
       <c r="E77" s="17"/>
       <c r="F77" s="17"/>
     </row>
     <row r="78" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="158"/>
-      <c r="B78" s="158"/>
-      <c r="C78" s="160"/>
-      <c r="D78" s="151"/>
+      <c r="A78" s="156"/>
+      <c r="B78" s="156"/>
+      <c r="C78" s="158"/>
+      <c r="D78" s="152"/>
       <c r="E78" s="17"/>
       <c r="F78" s="17"/>
     </row>
     <row r="79" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="158"/>
-      <c r="B79" s="158"/>
-      <c r="C79" s="160"/>
-      <c r="D79" s="151"/>
+      <c r="A79" s="156"/>
+      <c r="B79" s="156"/>
+      <c r="C79" s="158"/>
+      <c r="D79" s="152"/>
       <c r="E79" s="17"/>
       <c r="F79" s="17"/>
     </row>
     <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="158"/>
-      <c r="B80" s="158"/>
-      <c r="C80" s="160"/>
-      <c r="D80" s="151"/>
+      <c r="A80" s="156"/>
+      <c r="B80" s="156"/>
+      <c r="C80" s="158"/>
+      <c r="D80" s="152"/>
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="158"/>
-      <c r="B81" s="158"/>
-      <c r="C81" s="160"/>
-      <c r="D81" s="151"/>
+      <c r="A81" s="156"/>
+      <c r="B81" s="156"/>
+      <c r="C81" s="158"/>
+      <c r="D81" s="152"/>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="158"/>
-      <c r="B82" s="158"/>
-      <c r="C82" s="160"/>
-      <c r="D82" s="151"/>
+      <c r="A82" s="156"/>
+      <c r="B82" s="156"/>
+      <c r="C82" s="158"/>
+      <c r="D82" s="152"/>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="158"/>
-      <c r="B83" s="158"/>
-      <c r="C83" s="160"/>
-      <c r="D83" s="151"/>
+      <c r="A83" s="156"/>
+      <c r="B83" s="156"/>
+      <c r="C83" s="158"/>
+      <c r="D83" s="152"/>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="158"/>
-      <c r="B84" s="158"/>
-      <c r="C84" s="160"/>
-      <c r="D84" s="151"/>
+      <c r="A84" s="156"/>
+      <c r="B84" s="156"/>
+      <c r="C84" s="158"/>
+      <c r="D84" s="152"/>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="158"/>
-      <c r="B85" s="158"/>
-      <c r="C85" s="160"/>
-      <c r="D85" s="151"/>
+      <c r="A85" s="156"/>
+      <c r="B85" s="156"/>
+      <c r="C85" s="158"/>
+      <c r="D85" s="152"/>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="158"/>
-      <c r="B86" s="158"/>
-      <c r="C86" s="160"/>
-      <c r="D86" s="151"/>
+      <c r="A86" s="156"/>
+      <c r="B86" s="156"/>
+      <c r="C86" s="158"/>
+      <c r="D86" s="152"/>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="158"/>
-      <c r="B87" s="158"/>
-      <c r="C87" s="160"/>
-      <c r="D87" s="151"/>
+      <c r="A87" s="156"/>
+      <c r="B87" s="156"/>
+      <c r="C87" s="158"/>
+      <c r="D87" s="152"/>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="158"/>
-      <c r="B88" s="158"/>
-      <c r="C88" s="160"/>
-      <c r="D88" s="151"/>
+      <c r="A88" s="156"/>
+      <c r="B88" s="156"/>
+      <c r="C88" s="158"/>
+      <c r="D88" s="152"/>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="158"/>
-      <c r="B89" s="158"/>
-      <c r="C89" s="160"/>
-      <c r="D89" s="151"/>
+      <c r="A89" s="156"/>
+      <c r="B89" s="156"/>
+      <c r="C89" s="158"/>
+      <c r="D89" s="152"/>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="158"/>
-      <c r="B90" s="158"/>
-      <c r="C90" s="160"/>
-      <c r="D90" s="151"/>
+      <c r="A90" s="156"/>
+      <c r="B90" s="156"/>
+      <c r="C90" s="158"/>
+      <c r="D90" s="152"/>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="158"/>
-      <c r="B91" s="158"/>
-      <c r="C91" s="160"/>
-      <c r="D91" s="151"/>
+      <c r="A91" s="156"/>
+      <c r="B91" s="156"/>
+      <c r="C91" s="158"/>
+      <c r="D91" s="152"/>
     </row>
     <row r="92" spans="1:4" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="158"/>
-      <c r="B92" s="158"/>
-      <c r="C92" s="160"/>
-      <c r="D92" s="151"/>
+      <c r="A92" s="156"/>
+      <c r="B92" s="156"/>
+      <c r="C92" s="158"/>
+      <c r="D92" s="152"/>
     </row>
     <row r="93" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="143" t="s">
+      <c r="A93" s="159" t="s">
         <v>58</v>
       </c>
-      <c r="B93" s="144"/>
-      <c r="C93" s="144"/>
-      <c r="D93" s="145"/>
+      <c r="B93" s="160"/>
+      <c r="C93" s="160"/>
+      <c r="D93" s="161"/>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="146"/>
-      <c r="B94" s="130"/>
-      <c r="C94" s="130"/>
-      <c r="D94" s="131"/>
+      <c r="A94" s="162"/>
+      <c r="B94" s="73"/>
+      <c r="C94" s="73"/>
+      <c r="D94" s="74"/>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="129"/>
-      <c r="B95" s="130"/>
-      <c r="C95" s="130"/>
-      <c r="D95" s="131"/>
+      <c r="A95" s="72"/>
+      <c r="B95" s="73"/>
+      <c r="C95" s="73"/>
+      <c r="D95" s="74"/>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="129"/>
-      <c r="B96" s="130"/>
-      <c r="C96" s="130"/>
-      <c r="D96" s="131"/>
+      <c r="A96" s="72"/>
+      <c r="B96" s="73"/>
+      <c r="C96" s="73"/>
+      <c r="D96" s="74"/>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="132"/>
-      <c r="B97" s="133"/>
-      <c r="C97" s="133"/>
-      <c r="D97" s="134"/>
+      <c r="A97" s="75"/>
+      <c r="B97" s="76"/>
+      <c r="C97" s="76"/>
+      <c r="D97" s="77"/>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -30182,18 +30182,6 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A4:A20"/>
-    <mergeCell ref="B4:B20"/>
-    <mergeCell ref="C4:C20"/>
-    <mergeCell ref="D4:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A41:A57"/>
-    <mergeCell ref="A77:A92"/>
-    <mergeCell ref="B77:B92"/>
-    <mergeCell ref="C77:C92"/>
-    <mergeCell ref="D77:D92"/>
     <mergeCell ref="A93:D93"/>
     <mergeCell ref="A94:D97"/>
     <mergeCell ref="A23:A39"/>
@@ -30207,6 +30195,18 @@
     <mergeCell ref="B59:B75"/>
     <mergeCell ref="C59:C75"/>
     <mergeCell ref="D59:D75"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A41:A57"/>
+    <mergeCell ref="A77:A92"/>
+    <mergeCell ref="B77:B92"/>
+    <mergeCell ref="C77:C92"/>
+    <mergeCell ref="D77:D92"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="B4:B20"/>
+    <mergeCell ref="C4:C20"/>
+    <mergeCell ref="D4:D20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -30233,931 +30233,931 @@
   <sheetData>
     <row r="1" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9"/>
-      <c r="B1" s="189" t="s">
+      <c r="B1" s="166" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
       <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="167" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="156"/>
+      <c r="B2" s="168"/>
+      <c r="C2" s="167"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="147"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="181" t="s">
+      <c r="A3" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="170"/>
-      <c r="C3" s="193" t="s">
+      <c r="B3" s="173"/>
+      <c r="C3" s="174" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="182"/>
-      <c r="E3" s="194" t="s">
+      <c r="D3" s="175"/>
+      <c r="E3" s="176" t="s">
         <v>134</v>
       </c>
-      <c r="F3" s="170"/>
+      <c r="F3" s="173"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="169"/>
-      <c r="B4" s="170"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="170"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="170"/>
+      <c r="A4" s="177"/>
+      <c r="B4" s="173"/>
+      <c r="C4" s="177"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="177"/>
+      <c r="F4" s="173"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="129"/>
-      <c r="B5" s="131"/>
-      <c r="C5" s="129"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="131"/>
+      <c r="A5" s="72"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="74"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="129"/>
-      <c r="B6" s="131"/>
-      <c r="C6" s="129"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="131"/>
+      <c r="A6" s="72"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="74"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="129"/>
-      <c r="B7" s="131"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="131"/>
+      <c r="A7" s="72"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="74"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="129"/>
-      <c r="B8" s="131"/>
-      <c r="C8" s="129"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="129"/>
-      <c r="F8" s="131"/>
+      <c r="A8" s="72"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="74"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="129"/>
-      <c r="B9" s="131"/>
-      <c r="C9" s="129"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="131"/>
+      <c r="A9" s="72"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="74"/>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="129"/>
-      <c r="B10" s="131"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="131"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="74"/>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="129"/>
-      <c r="B11" s="131"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="131"/>
+      <c r="A11" s="72"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="74"/>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="129"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="131"/>
+      <c r="A12" s="72"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="74"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="129"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="129"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="131"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="74"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="129"/>
-      <c r="B14" s="131"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="131"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="74"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="129"/>
-      <c r="B15" s="131"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="131"/>
+      <c r="A15" s="72"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="74"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="129"/>
-      <c r="B16" s="131"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="131"/>
+      <c r="A16" s="72"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="74"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="129"/>
-      <c r="B17" s="131"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="131"/>
+      <c r="A17" s="72"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="74"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="129"/>
-      <c r="B18" s="131"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="131"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="131"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="74"/>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="129"/>
-      <c r="B19" s="131"/>
-      <c r="C19" s="129"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="131"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="74"/>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="132"/>
-      <c r="B20" s="134"/>
-      <c r="C20" s="132"/>
-      <c r="D20" s="134"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="134"/>
+      <c r="A20" s="75"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="77"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="171" t="s">
+      <c r="A21" s="178" t="s">
         <v>135</v>
       </c>
-      <c r="B21" s="166"/>
-      <c r="C21" s="171" t="s">
+      <c r="B21" s="179"/>
+      <c r="C21" s="178" t="s">
         <v>136</v>
       </c>
-      <c r="D21" s="166"/>
-      <c r="E21" s="171" t="s">
+      <c r="D21" s="179"/>
+      <c r="E21" s="178" t="s">
         <v>137</v>
       </c>
-      <c r="F21" s="166"/>
+      <c r="F21" s="179"/>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="169"/>
-      <c r="B22" s="170"/>
-      <c r="C22" s="176"/>
-      <c r="D22" s="130"/>
-      <c r="E22" s="169"/>
-      <c r="F22" s="170"/>
+      <c r="A22" s="177"/>
+      <c r="B22" s="173"/>
+      <c r="C22" s="190"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="177"/>
+      <c r="F22" s="173"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="129"/>
-      <c r="B23" s="131"/>
-      <c r="C23" s="130"/>
-      <c r="D23" s="130"/>
-      <c r="E23" s="129"/>
-      <c r="F23" s="131"/>
+      <c r="A23" s="72"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="74"/>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="129"/>
-      <c r="B24" s="131"/>
-      <c r="C24" s="130"/>
-      <c r="D24" s="130"/>
-      <c r="E24" s="129"/>
-      <c r="F24" s="131"/>
+      <c r="A24" s="72"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="74"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="129"/>
-      <c r="B25" s="131"/>
-      <c r="C25" s="130"/>
-      <c r="D25" s="130"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="131"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="74"/>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="129"/>
-      <c r="B26" s="131"/>
-      <c r="C26" s="130"/>
-      <c r="D26" s="130"/>
-      <c r="E26" s="129"/>
-      <c r="F26" s="131"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="74"/>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="129"/>
-      <c r="B27" s="131"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="130"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="131"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="74"/>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="129"/>
-      <c r="B28" s="131"/>
-      <c r="C28" s="130"/>
-      <c r="D28" s="130"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="131"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="74"/>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="129"/>
-      <c r="B29" s="131"/>
-      <c r="C29" s="130"/>
-      <c r="D29" s="130"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="131"/>
+      <c r="A29" s="72"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="74"/>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="129"/>
-      <c r="B30" s="131"/>
-      <c r="C30" s="130"/>
-      <c r="D30" s="130"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="131"/>
+      <c r="A30" s="72"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="74"/>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="129"/>
-      <c r="B31" s="131"/>
-      <c r="C31" s="130"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="129"/>
-      <c r="F31" s="131"/>
+      <c r="A31" s="72"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="74"/>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="129"/>
-      <c r="B32" s="131"/>
-      <c r="C32" s="130"/>
-      <c r="D32" s="130"/>
-      <c r="E32" s="129"/>
-      <c r="F32" s="131"/>
+      <c r="A32" s="72"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="74"/>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="129"/>
-      <c r="B33" s="131"/>
-      <c r="C33" s="130"/>
-      <c r="D33" s="130"/>
-      <c r="E33" s="129"/>
-      <c r="F33" s="131"/>
+      <c r="A33" s="72"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="74"/>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="129"/>
-      <c r="B34" s="131"/>
-      <c r="C34" s="130"/>
-      <c r="D34" s="130"/>
-      <c r="E34" s="129"/>
-      <c r="F34" s="131"/>
+      <c r="A34" s="72"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="74"/>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="129"/>
-      <c r="B35" s="131"/>
-      <c r="C35" s="130"/>
-      <c r="D35" s="130"/>
-      <c r="E35" s="129"/>
-      <c r="F35" s="131"/>
+      <c r="A35" s="72"/>
+      <c r="B35" s="74"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="74"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="129"/>
-      <c r="B36" s="131"/>
-      <c r="C36" s="130"/>
-      <c r="D36" s="130"/>
-      <c r="E36" s="129"/>
-      <c r="F36" s="131"/>
+      <c r="A36" s="72"/>
+      <c r="B36" s="74"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="74"/>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="129"/>
-      <c r="B37" s="131"/>
-      <c r="C37" s="130"/>
-      <c r="D37" s="130"/>
-      <c r="E37" s="129"/>
-      <c r="F37" s="131"/>
+      <c r="A37" s="72"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="74"/>
     </row>
     <row r="38" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="132"/>
-      <c r="B38" s="134"/>
-      <c r="C38" s="130"/>
-      <c r="D38" s="130"/>
-      <c r="E38" s="132"/>
-      <c r="F38" s="134"/>
+      <c r="A38" s="75"/>
+      <c r="B38" s="77"/>
+      <c r="C38" s="73"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="77"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="171" t="s">
+      <c r="A39" s="178" t="s">
         <v>138</v>
       </c>
-      <c r="B39" s="166"/>
-      <c r="C39" s="171" t="s">
+      <c r="B39" s="179"/>
+      <c r="C39" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="166"/>
-      <c r="E39" s="171" t="s">
+      <c r="D39" s="179"/>
+      <c r="E39" s="178" t="s">
         <v>139</v>
       </c>
-      <c r="F39" s="166"/>
+      <c r="F39" s="179"/>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="169"/>
-      <c r="B40" s="172"/>
-      <c r="C40" s="169"/>
-      <c r="D40" s="172"/>
-      <c r="E40" s="169"/>
-      <c r="F40" s="172"/>
+      <c r="A40" s="177"/>
+      <c r="B40" s="191"/>
+      <c r="C40" s="177"/>
+      <c r="D40" s="191"/>
+      <c r="E40" s="177"/>
+      <c r="F40" s="191"/>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="167"/>
-      <c r="B41" s="173"/>
-      <c r="C41" s="167"/>
-      <c r="D41" s="173"/>
-      <c r="E41" s="167"/>
-      <c r="F41" s="173"/>
+      <c r="A41" s="182"/>
+      <c r="B41" s="192"/>
+      <c r="C41" s="182"/>
+      <c r="D41" s="192"/>
+      <c r="E41" s="182"/>
+      <c r="F41" s="192"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="167"/>
-      <c r="B42" s="173"/>
-      <c r="C42" s="167"/>
-      <c r="D42" s="173"/>
-      <c r="E42" s="167"/>
-      <c r="F42" s="173"/>
+      <c r="A42" s="182"/>
+      <c r="B42" s="192"/>
+      <c r="C42" s="182"/>
+      <c r="D42" s="192"/>
+      <c r="E42" s="182"/>
+      <c r="F42" s="192"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="167"/>
-      <c r="B43" s="173"/>
-      <c r="C43" s="167"/>
-      <c r="D43" s="173"/>
-      <c r="E43" s="167"/>
-      <c r="F43" s="173"/>
+      <c r="A43" s="182"/>
+      <c r="B43" s="192"/>
+      <c r="C43" s="182"/>
+      <c r="D43" s="192"/>
+      <c r="E43" s="182"/>
+      <c r="F43" s="192"/>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="167"/>
-      <c r="B44" s="173"/>
-      <c r="C44" s="167"/>
-      <c r="D44" s="173"/>
-      <c r="E44" s="167"/>
-      <c r="F44" s="173"/>
+      <c r="A44" s="182"/>
+      <c r="B44" s="192"/>
+      <c r="C44" s="182"/>
+      <c r="D44" s="192"/>
+      <c r="E44" s="182"/>
+      <c r="F44" s="192"/>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="167"/>
-      <c r="B45" s="173"/>
-      <c r="C45" s="167"/>
-      <c r="D45" s="173"/>
-      <c r="E45" s="167"/>
-      <c r="F45" s="173"/>
+      <c r="A45" s="182"/>
+      <c r="B45" s="192"/>
+      <c r="C45" s="182"/>
+      <c r="D45" s="192"/>
+      <c r="E45" s="182"/>
+      <c r="F45" s="192"/>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="167"/>
-      <c r="B46" s="173"/>
-      <c r="C46" s="167"/>
-      <c r="D46" s="173"/>
-      <c r="E46" s="167"/>
-      <c r="F46" s="173"/>
+      <c r="A46" s="182"/>
+      <c r="B46" s="192"/>
+      <c r="C46" s="182"/>
+      <c r="D46" s="192"/>
+      <c r="E46" s="182"/>
+      <c r="F46" s="192"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="167"/>
-      <c r="B47" s="173"/>
-      <c r="C47" s="167"/>
-      <c r="D47" s="173"/>
-      <c r="E47" s="167"/>
-      <c r="F47" s="173"/>
+      <c r="A47" s="182"/>
+      <c r="B47" s="192"/>
+      <c r="C47" s="182"/>
+      <c r="D47" s="192"/>
+      <c r="E47" s="182"/>
+      <c r="F47" s="192"/>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="167"/>
-      <c r="B48" s="173"/>
-      <c r="C48" s="167"/>
-      <c r="D48" s="173"/>
-      <c r="E48" s="167"/>
-      <c r="F48" s="173"/>
+      <c r="A48" s="182"/>
+      <c r="B48" s="192"/>
+      <c r="C48" s="182"/>
+      <c r="D48" s="192"/>
+      <c r="E48" s="182"/>
+      <c r="F48" s="192"/>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="167"/>
-      <c r="B49" s="173"/>
-      <c r="C49" s="167"/>
-      <c r="D49" s="173"/>
-      <c r="E49" s="167"/>
-      <c r="F49" s="173"/>
+      <c r="A49" s="182"/>
+      <c r="B49" s="192"/>
+      <c r="C49" s="182"/>
+      <c r="D49" s="192"/>
+      <c r="E49" s="182"/>
+      <c r="F49" s="192"/>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="167"/>
-      <c r="B50" s="173"/>
-      <c r="C50" s="167"/>
-      <c r="D50" s="173"/>
-      <c r="E50" s="167"/>
-      <c r="F50" s="173"/>
+      <c r="A50" s="182"/>
+      <c r="B50" s="192"/>
+      <c r="C50" s="182"/>
+      <c r="D50" s="192"/>
+      <c r="E50" s="182"/>
+      <c r="F50" s="192"/>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="167"/>
-      <c r="B51" s="173"/>
-      <c r="C51" s="167"/>
-      <c r="D51" s="173"/>
-      <c r="E51" s="167"/>
-      <c r="F51" s="173"/>
+      <c r="A51" s="182"/>
+      <c r="B51" s="192"/>
+      <c r="C51" s="182"/>
+      <c r="D51" s="192"/>
+      <c r="E51" s="182"/>
+      <c r="F51" s="192"/>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="167"/>
-      <c r="B52" s="173"/>
-      <c r="C52" s="167"/>
-      <c r="D52" s="173"/>
-      <c r="E52" s="167"/>
-      <c r="F52" s="173"/>
+      <c r="A52" s="182"/>
+      <c r="B52" s="192"/>
+      <c r="C52" s="182"/>
+      <c r="D52" s="192"/>
+      <c r="E52" s="182"/>
+      <c r="F52" s="192"/>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="167"/>
-      <c r="B53" s="173"/>
-      <c r="C53" s="167"/>
-      <c r="D53" s="173"/>
-      <c r="E53" s="167"/>
-      <c r="F53" s="173"/>
+      <c r="A53" s="182"/>
+      <c r="B53" s="192"/>
+      <c r="C53" s="182"/>
+      <c r="D53" s="192"/>
+      <c r="E53" s="182"/>
+      <c r="F53" s="192"/>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="167"/>
-      <c r="B54" s="173"/>
-      <c r="C54" s="167"/>
-      <c r="D54" s="173"/>
-      <c r="E54" s="167"/>
-      <c r="F54" s="173"/>
+      <c r="A54" s="182"/>
+      <c r="B54" s="192"/>
+      <c r="C54" s="182"/>
+      <c r="D54" s="192"/>
+      <c r="E54" s="182"/>
+      <c r="F54" s="192"/>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="167"/>
-      <c r="B55" s="173"/>
-      <c r="C55" s="167"/>
-      <c r="D55" s="173"/>
-      <c r="E55" s="167"/>
-      <c r="F55" s="173"/>
+      <c r="A55" s="182"/>
+      <c r="B55" s="192"/>
+      <c r="C55" s="182"/>
+      <c r="D55" s="192"/>
+      <c r="E55" s="182"/>
+      <c r="F55" s="192"/>
     </row>
     <row r="56" spans="1:6" ht="19.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="174"/>
-      <c r="B56" s="175"/>
-      <c r="C56" s="174"/>
-      <c r="D56" s="175"/>
-      <c r="E56" s="174"/>
-      <c r="F56" s="175"/>
+      <c r="A56" s="193"/>
+      <c r="B56" s="194"/>
+      <c r="C56" s="193"/>
+      <c r="D56" s="194"/>
+      <c r="E56" s="193"/>
+      <c r="F56" s="194"/>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="165" t="s">
+      <c r="A57" s="167" t="s">
         <v>140</v>
       </c>
-      <c r="B57" s="166"/>
-      <c r="C57" s="165" t="s">
+      <c r="B57" s="179"/>
+      <c r="C57" s="167" t="s">
         <v>65</v>
       </c>
-      <c r="D57" s="166"/>
-      <c r="E57" s="165" t="s">
+      <c r="D57" s="179"/>
+      <c r="E57" s="167" t="s">
         <v>66</v>
       </c>
-      <c r="F57" s="166"/>
+      <c r="F57" s="179"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="167"/>
-      <c r="B58" s="168"/>
-      <c r="C58" s="167"/>
-      <c r="D58" s="130"/>
-      <c r="E58" s="169"/>
-      <c r="F58" s="170"/>
+      <c r="A58" s="182"/>
+      <c r="B58" s="183"/>
+      <c r="C58" s="182"/>
+      <c r="D58" s="73"/>
+      <c r="E58" s="177"/>
+      <c r="F58" s="173"/>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="129"/>
-      <c r="B59" s="168"/>
-      <c r="C59" s="129"/>
-      <c r="D59" s="130"/>
-      <c r="E59" s="129"/>
-      <c r="F59" s="131"/>
+      <c r="A59" s="72"/>
+      <c r="B59" s="183"/>
+      <c r="C59" s="72"/>
+      <c r="D59" s="73"/>
+      <c r="E59" s="72"/>
+      <c r="F59" s="74"/>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="129"/>
-      <c r="B60" s="168"/>
-      <c r="C60" s="129"/>
-      <c r="D60" s="130"/>
-      <c r="E60" s="129"/>
-      <c r="F60" s="131"/>
+      <c r="A60" s="72"/>
+      <c r="B60" s="183"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="73"/>
+      <c r="E60" s="72"/>
+      <c r="F60" s="74"/>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="129"/>
-      <c r="B61" s="168"/>
-      <c r="C61" s="129"/>
-      <c r="D61" s="130"/>
-      <c r="E61" s="129"/>
-      <c r="F61" s="131"/>
+      <c r="A61" s="72"/>
+      <c r="B61" s="183"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="72"/>
+      <c r="F61" s="74"/>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="129"/>
-      <c r="B62" s="168"/>
-      <c r="C62" s="129"/>
-      <c r="D62" s="130"/>
-      <c r="E62" s="129"/>
-      <c r="F62" s="131"/>
+      <c r="A62" s="72"/>
+      <c r="B62" s="183"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="73"/>
+      <c r="E62" s="72"/>
+      <c r="F62" s="74"/>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="129"/>
-      <c r="B63" s="168"/>
-      <c r="C63" s="129"/>
-      <c r="D63" s="130"/>
-      <c r="E63" s="129"/>
-      <c r="F63" s="131"/>
+      <c r="A63" s="72"/>
+      <c r="B63" s="183"/>
+      <c r="C63" s="72"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="72"/>
+      <c r="F63" s="74"/>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="129"/>
-      <c r="B64" s="168"/>
-      <c r="C64" s="129"/>
-      <c r="D64" s="130"/>
-      <c r="E64" s="129"/>
-      <c r="F64" s="131"/>
+      <c r="A64" s="72"/>
+      <c r="B64" s="183"/>
+      <c r="C64" s="72"/>
+      <c r="D64" s="73"/>
+      <c r="E64" s="72"/>
+      <c r="F64" s="74"/>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="129"/>
-      <c r="B65" s="168"/>
-      <c r="C65" s="129"/>
-      <c r="D65" s="130"/>
-      <c r="E65" s="129"/>
-      <c r="F65" s="131"/>
+      <c r="A65" s="72"/>
+      <c r="B65" s="183"/>
+      <c r="C65" s="72"/>
+      <c r="D65" s="73"/>
+      <c r="E65" s="72"/>
+      <c r="F65" s="74"/>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="129"/>
-      <c r="B66" s="168"/>
-      <c r="C66" s="129"/>
-      <c r="D66" s="130"/>
-      <c r="E66" s="129"/>
-      <c r="F66" s="131"/>
+      <c r="A66" s="72"/>
+      <c r="B66" s="183"/>
+      <c r="C66" s="72"/>
+      <c r="D66" s="73"/>
+      <c r="E66" s="72"/>
+      <c r="F66" s="74"/>
     </row>
     <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="129"/>
-      <c r="B67" s="168"/>
-      <c r="C67" s="129"/>
-      <c r="D67" s="130"/>
-      <c r="E67" s="129"/>
-      <c r="F67" s="131"/>
+      <c r="A67" s="72"/>
+      <c r="B67" s="183"/>
+      <c r="C67" s="72"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="74"/>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="129"/>
-      <c r="B68" s="168"/>
-      <c r="C68" s="129"/>
-      <c r="D68" s="130"/>
-      <c r="E68" s="129"/>
-      <c r="F68" s="131"/>
+      <c r="A68" s="72"/>
+      <c r="B68" s="183"/>
+      <c r="C68" s="72"/>
+      <c r="D68" s="73"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="74"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="129"/>
-      <c r="B69" s="168"/>
-      <c r="C69" s="129"/>
-      <c r="D69" s="130"/>
-      <c r="E69" s="129"/>
-      <c r="F69" s="131"/>
+      <c r="A69" s="72"/>
+      <c r="B69" s="183"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="73"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="74"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="129"/>
-      <c r="B70" s="168"/>
-      <c r="C70" s="129"/>
-      <c r="D70" s="130"/>
-      <c r="E70" s="129"/>
-      <c r="F70" s="131"/>
+      <c r="A70" s="72"/>
+      <c r="B70" s="183"/>
+      <c r="C70" s="72"/>
+      <c r="D70" s="73"/>
+      <c r="E70" s="72"/>
+      <c r="F70" s="74"/>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="129"/>
-      <c r="B71" s="168"/>
-      <c r="C71" s="129"/>
-      <c r="D71" s="130"/>
-      <c r="E71" s="129"/>
-      <c r="F71" s="131"/>
+      <c r="A71" s="72"/>
+      <c r="B71" s="183"/>
+      <c r="C71" s="72"/>
+      <c r="D71" s="73"/>
+      <c r="E71" s="72"/>
+      <c r="F71" s="74"/>
     </row>
     <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="129"/>
-      <c r="B72" s="168"/>
-      <c r="C72" s="129"/>
-      <c r="D72" s="130"/>
-      <c r="E72" s="129"/>
-      <c r="F72" s="131"/>
+      <c r="A72" s="72"/>
+      <c r="B72" s="183"/>
+      <c r="C72" s="72"/>
+      <c r="D72" s="73"/>
+      <c r="E72" s="72"/>
+      <c r="F72" s="74"/>
     </row>
     <row r="73" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="129"/>
-      <c r="B73" s="168"/>
-      <c r="C73" s="129"/>
-      <c r="D73" s="130"/>
-      <c r="E73" s="129"/>
-      <c r="F73" s="131"/>
+      <c r="A73" s="72"/>
+      <c r="B73" s="183"/>
+      <c r="C73" s="72"/>
+      <c r="D73" s="73"/>
+      <c r="E73" s="72"/>
+      <c r="F73" s="74"/>
     </row>
     <row r="74" spans="1:6" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="129"/>
-      <c r="B74" s="168"/>
-      <c r="C74" s="129"/>
-      <c r="D74" s="130"/>
-      <c r="E74" s="129"/>
-      <c r="F74" s="131"/>
+      <c r="A74" s="72"/>
+      <c r="B74" s="183"/>
+      <c r="C74" s="72"/>
+      <c r="D74" s="73"/>
+      <c r="E74" s="72"/>
+      <c r="F74" s="74"/>
     </row>
     <row r="75" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="165" t="s">
+      <c r="A75" s="167" t="s">
         <v>61</v>
       </c>
-      <c r="B75" s="191"/>
-      <c r="C75" s="165" t="s">
+      <c r="B75" s="169"/>
+      <c r="C75" s="167" t="s">
         <v>62</v>
       </c>
-      <c r="D75" s="192"/>
-      <c r="E75" s="165" t="s">
+      <c r="D75" s="170"/>
+      <c r="E75" s="167" t="s">
         <v>63</v>
       </c>
-      <c r="F75" s="178"/>
+      <c r="F75" s="171"/>
     </row>
     <row r="76" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="187"/>
-      <c r="B76" s="128"/>
-      <c r="C76" s="187"/>
-      <c r="D76" s="128"/>
-      <c r="E76" s="188"/>
-      <c r="F76" s="128"/>
+      <c r="A76" s="164"/>
+      <c r="B76" s="71"/>
+      <c r="C76" s="164"/>
+      <c r="D76" s="71"/>
+      <c r="E76" s="165"/>
+      <c r="F76" s="71"/>
     </row>
     <row r="77" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="129"/>
-      <c r="B77" s="131"/>
-      <c r="C77" s="129"/>
-      <c r="D77" s="131"/>
-      <c r="E77" s="130"/>
-      <c r="F77" s="131"/>
+      <c r="A77" s="72"/>
+      <c r="B77" s="74"/>
+      <c r="C77" s="72"/>
+      <c r="D77" s="74"/>
+      <c r="E77" s="73"/>
+      <c r="F77" s="74"/>
     </row>
     <row r="78" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="129"/>
-      <c r="B78" s="131"/>
-      <c r="C78" s="129"/>
-      <c r="D78" s="131"/>
-      <c r="E78" s="130"/>
-      <c r="F78" s="131"/>
+      <c r="A78" s="72"/>
+      <c r="B78" s="74"/>
+      <c r="C78" s="72"/>
+      <c r="D78" s="74"/>
+      <c r="E78" s="73"/>
+      <c r="F78" s="74"/>
     </row>
     <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="129"/>
-      <c r="B79" s="131"/>
-      <c r="C79" s="129"/>
-      <c r="D79" s="131"/>
-      <c r="E79" s="130"/>
-      <c r="F79" s="131"/>
+      <c r="A79" s="72"/>
+      <c r="B79" s="74"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="74"/>
+      <c r="E79" s="73"/>
+      <c r="F79" s="74"/>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="129"/>
-      <c r="B80" s="131"/>
-      <c r="C80" s="129"/>
-      <c r="D80" s="131"/>
-      <c r="E80" s="130"/>
-      <c r="F80" s="131"/>
+      <c r="A80" s="72"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="74"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="129"/>
-      <c r="B81" s="131"/>
-      <c r="C81" s="129"/>
-      <c r="D81" s="131"/>
-      <c r="E81" s="130"/>
-      <c r="F81" s="131"/>
+      <c r="A81" s="72"/>
+      <c r="B81" s="74"/>
+      <c r="C81" s="72"/>
+      <c r="D81" s="74"/>
+      <c r="E81" s="73"/>
+      <c r="F81" s="74"/>
     </row>
     <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="129"/>
-      <c r="B82" s="131"/>
-      <c r="C82" s="129"/>
-      <c r="D82" s="131"/>
-      <c r="E82" s="130"/>
-      <c r="F82" s="131"/>
+      <c r="A82" s="72"/>
+      <c r="B82" s="74"/>
+      <c r="C82" s="72"/>
+      <c r="D82" s="74"/>
+      <c r="E82" s="73"/>
+      <c r="F82" s="74"/>
     </row>
     <row r="83" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="129"/>
-      <c r="B83" s="131"/>
-      <c r="C83" s="129"/>
-      <c r="D83" s="131"/>
-      <c r="E83" s="130"/>
-      <c r="F83" s="131"/>
+      <c r="A83" s="72"/>
+      <c r="B83" s="74"/>
+      <c r="C83" s="72"/>
+      <c r="D83" s="74"/>
+      <c r="E83" s="73"/>
+      <c r="F83" s="74"/>
     </row>
     <row r="84" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="129"/>
-      <c r="B84" s="131"/>
-      <c r="C84" s="129"/>
-      <c r="D84" s="131"/>
-      <c r="E84" s="130"/>
-      <c r="F84" s="131"/>
+      <c r="A84" s="72"/>
+      <c r="B84" s="74"/>
+      <c r="C84" s="72"/>
+      <c r="D84" s="74"/>
+      <c r="E84" s="73"/>
+      <c r="F84" s="74"/>
     </row>
     <row r="85" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="129"/>
-      <c r="B85" s="131"/>
-      <c r="C85" s="129"/>
-      <c r="D85" s="131"/>
-      <c r="E85" s="130"/>
-      <c r="F85" s="131"/>
+      <c r="A85" s="72"/>
+      <c r="B85" s="74"/>
+      <c r="C85" s="72"/>
+      <c r="D85" s="74"/>
+      <c r="E85" s="73"/>
+      <c r="F85" s="74"/>
     </row>
     <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="129"/>
-      <c r="B86" s="131"/>
-      <c r="C86" s="129"/>
-      <c r="D86" s="131"/>
-      <c r="E86" s="130"/>
-      <c r="F86" s="131"/>
+      <c r="A86" s="72"/>
+      <c r="B86" s="74"/>
+      <c r="C86" s="72"/>
+      <c r="D86" s="74"/>
+      <c r="E86" s="73"/>
+      <c r="F86" s="74"/>
     </row>
     <row r="87" spans="1:6" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="129"/>
-      <c r="B87" s="131"/>
-      <c r="C87" s="129"/>
-      <c r="D87" s="131"/>
-      <c r="E87" s="130"/>
-      <c r="F87" s="131"/>
+      <c r="A87" s="72"/>
+      <c r="B87" s="74"/>
+      <c r="C87" s="72"/>
+      <c r="D87" s="74"/>
+      <c r="E87" s="73"/>
+      <c r="F87" s="74"/>
     </row>
     <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="129"/>
-      <c r="B88" s="131"/>
-      <c r="C88" s="129"/>
-      <c r="D88" s="131"/>
-      <c r="E88" s="130"/>
-      <c r="F88" s="131"/>
+      <c r="A88" s="72"/>
+      <c r="B88" s="74"/>
+      <c r="C88" s="72"/>
+      <c r="D88" s="74"/>
+      <c r="E88" s="73"/>
+      <c r="F88" s="74"/>
     </row>
     <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="129"/>
-      <c r="B89" s="131"/>
-      <c r="C89" s="129"/>
-      <c r="D89" s="131"/>
-      <c r="E89" s="130"/>
-      <c r="F89" s="131"/>
+      <c r="A89" s="72"/>
+      <c r="B89" s="74"/>
+      <c r="C89" s="72"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="73"/>
+      <c r="F89" s="74"/>
     </row>
     <row r="90" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="129"/>
-      <c r="B90" s="131"/>
-      <c r="C90" s="129"/>
-      <c r="D90" s="131"/>
-      <c r="E90" s="130"/>
-      <c r="F90" s="131"/>
+      <c r="A90" s="72"/>
+      <c r="B90" s="74"/>
+      <c r="C90" s="72"/>
+      <c r="D90" s="74"/>
+      <c r="E90" s="73"/>
+      <c r="F90" s="74"/>
     </row>
     <row r="91" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="129"/>
-      <c r="B91" s="131"/>
-      <c r="C91" s="129"/>
-      <c r="D91" s="131"/>
-      <c r="E91" s="130"/>
-      <c r="F91" s="131"/>
+      <c r="A91" s="72"/>
+      <c r="B91" s="74"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="74"/>
+      <c r="E91" s="73"/>
+      <c r="F91" s="74"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="129"/>
-      <c r="B92" s="131"/>
-      <c r="C92" s="129"/>
-      <c r="D92" s="131"/>
-      <c r="E92" s="130"/>
-      <c r="F92" s="131"/>
+      <c r="A92" s="72"/>
+      <c r="B92" s="74"/>
+      <c r="C92" s="72"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="73"/>
+      <c r="F92" s="74"/>
     </row>
     <row r="93" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="132"/>
-      <c r="B93" s="134"/>
-      <c r="C93" s="132"/>
-      <c r="D93" s="134"/>
-      <c r="E93" s="133"/>
-      <c r="F93" s="134"/>
+      <c r="A93" s="75"/>
+      <c r="B93" s="77"/>
+      <c r="C93" s="75"/>
+      <c r="D93" s="77"/>
+      <c r="E93" s="76"/>
+      <c r="F93" s="77"/>
     </row>
     <row r="94" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="165" t="s">
+      <c r="A94" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="B94" s="178"/>
+      <c r="B94" s="171"/>
       <c r="C94" s="180" t="s">
         <v>65</v>
       </c>
-      <c r="D94" s="178"/>
-      <c r="E94" s="183" t="s">
+      <c r="D94" s="171"/>
+      <c r="E94" s="181" t="s">
         <v>66</v>
       </c>
-      <c r="F94" s="178"/>
+      <c r="F94" s="171"/>
     </row>
     <row r="95" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="167"/>
-      <c r="B95" s="168"/>
-      <c r="C95" s="167"/>
-      <c r="D95" s="168"/>
-      <c r="E95" s="167"/>
-      <c r="F95" s="131"/>
+      <c r="A95" s="182"/>
+      <c r="B95" s="183"/>
+      <c r="C95" s="182"/>
+      <c r="D95" s="183"/>
+      <c r="E95" s="182"/>
+      <c r="F95" s="74"/>
     </row>
     <row r="96" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="129"/>
-      <c r="B96" s="168"/>
-      <c r="C96" s="129"/>
-      <c r="D96" s="168"/>
-      <c r="E96" s="129"/>
-      <c r="F96" s="131"/>
+      <c r="A96" s="72"/>
+      <c r="B96" s="183"/>
+      <c r="C96" s="72"/>
+      <c r="D96" s="183"/>
+      <c r="E96" s="72"/>
+      <c r="F96" s="74"/>
     </row>
     <row r="97" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="129"/>
-      <c r="B97" s="168"/>
-      <c r="C97" s="129"/>
-      <c r="D97" s="168"/>
-      <c r="E97" s="129"/>
-      <c r="F97" s="131"/>
+      <c r="A97" s="72"/>
+      <c r="B97" s="183"/>
+      <c r="C97" s="72"/>
+      <c r="D97" s="183"/>
+      <c r="E97" s="72"/>
+      <c r="F97" s="74"/>
     </row>
     <row r="98" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="129"/>
-      <c r="B98" s="168"/>
-      <c r="C98" s="129"/>
-      <c r="D98" s="168"/>
-      <c r="E98" s="129"/>
-      <c r="F98" s="131"/>
+      <c r="A98" s="72"/>
+      <c r="B98" s="183"/>
+      <c r="C98" s="72"/>
+      <c r="D98" s="183"/>
+      <c r="E98" s="72"/>
+      <c r="F98" s="74"/>
     </row>
     <row r="99" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="129"/>
-      <c r="B99" s="168"/>
-      <c r="C99" s="129"/>
-      <c r="D99" s="168"/>
-      <c r="E99" s="129"/>
-      <c r="F99" s="131"/>
+      <c r="A99" s="72"/>
+      <c r="B99" s="183"/>
+      <c r="C99" s="72"/>
+      <c r="D99" s="183"/>
+      <c r="E99" s="72"/>
+      <c r="F99" s="74"/>
     </row>
     <row r="100" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="129"/>
-      <c r="B100" s="168"/>
-      <c r="C100" s="129"/>
-      <c r="D100" s="168"/>
-      <c r="E100" s="129"/>
-      <c r="F100" s="131"/>
+      <c r="A100" s="72"/>
+      <c r="B100" s="183"/>
+      <c r="C100" s="72"/>
+      <c r="D100" s="183"/>
+      <c r="E100" s="72"/>
+      <c r="F100" s="74"/>
     </row>
     <row r="101" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="129"/>
-      <c r="B101" s="168"/>
-      <c r="C101" s="129"/>
-      <c r="D101" s="168"/>
-      <c r="E101" s="129"/>
-      <c r="F101" s="131"/>
+      <c r="A101" s="72"/>
+      <c r="B101" s="183"/>
+      <c r="C101" s="72"/>
+      <c r="D101" s="183"/>
+      <c r="E101" s="72"/>
+      <c r="F101" s="74"/>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="129"/>
-      <c r="B102" s="168"/>
-      <c r="C102" s="129"/>
-      <c r="D102" s="168"/>
-      <c r="E102" s="129"/>
-      <c r="F102" s="131"/>
+      <c r="A102" s="72"/>
+      <c r="B102" s="183"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="183"/>
+      <c r="E102" s="72"/>
+      <c r="F102" s="74"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="129"/>
-      <c r="B103" s="168"/>
-      <c r="C103" s="129"/>
-      <c r="D103" s="168"/>
-      <c r="E103" s="129"/>
-      <c r="F103" s="131"/>
+      <c r="A103" s="72"/>
+      <c r="B103" s="183"/>
+      <c r="C103" s="72"/>
+      <c r="D103" s="183"/>
+      <c r="E103" s="72"/>
+      <c r="F103" s="74"/>
     </row>
     <row r="104" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="129"/>
-      <c r="B104" s="168"/>
-      <c r="C104" s="129"/>
-      <c r="D104" s="168"/>
-      <c r="E104" s="129"/>
-      <c r="F104" s="131"/>
+      <c r="A104" s="72"/>
+      <c r="B104" s="183"/>
+      <c r="C104" s="72"/>
+      <c r="D104" s="183"/>
+      <c r="E104" s="72"/>
+      <c r="F104" s="74"/>
     </row>
     <row r="105" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="129"/>
-      <c r="B105" s="168"/>
-      <c r="C105" s="129"/>
-      <c r="D105" s="168"/>
-      <c r="E105" s="129"/>
-      <c r="F105" s="131"/>
+      <c r="A105" s="72"/>
+      <c r="B105" s="183"/>
+      <c r="C105" s="72"/>
+      <c r="D105" s="183"/>
+      <c r="E105" s="72"/>
+      <c r="F105" s="74"/>
     </row>
     <row r="106" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="129"/>
-      <c r="B106" s="168"/>
-      <c r="C106" s="129"/>
-      <c r="D106" s="168"/>
-      <c r="E106" s="129"/>
-      <c r="F106" s="131"/>
+      <c r="A106" s="72"/>
+      <c r="B106" s="183"/>
+      <c r="C106" s="72"/>
+      <c r="D106" s="183"/>
+      <c r="E106" s="72"/>
+      <c r="F106" s="74"/>
     </row>
     <row r="107" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="129"/>
-      <c r="B107" s="168"/>
-      <c r="C107" s="129"/>
-      <c r="D107" s="168"/>
-      <c r="E107" s="129"/>
-      <c r="F107" s="131"/>
+      <c r="A107" s="72"/>
+      <c r="B107" s="183"/>
+      <c r="C107" s="72"/>
+      <c r="D107" s="183"/>
+      <c r="E107" s="72"/>
+      <c r="F107" s="74"/>
     </row>
     <row r="108" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="129"/>
-      <c r="B108" s="168"/>
-      <c r="C108" s="129"/>
-      <c r="D108" s="168"/>
-      <c r="E108" s="129"/>
-      <c r="F108" s="131"/>
+      <c r="A108" s="72"/>
+      <c r="B108" s="183"/>
+      <c r="C108" s="72"/>
+      <c r="D108" s="183"/>
+      <c r="E108" s="72"/>
+      <c r="F108" s="74"/>
     </row>
     <row r="109" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="129"/>
-      <c r="B109" s="168"/>
-      <c r="C109" s="129"/>
-      <c r="D109" s="168"/>
-      <c r="E109" s="129"/>
-      <c r="F109" s="131"/>
+      <c r="A109" s="72"/>
+      <c r="B109" s="183"/>
+      <c r="C109" s="72"/>
+      <c r="D109" s="183"/>
+      <c r="E109" s="72"/>
+      <c r="F109" s="74"/>
     </row>
     <row r="110" spans="1:6" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="129"/>
-      <c r="B110" s="168"/>
-      <c r="C110" s="129"/>
-      <c r="D110" s="168"/>
-      <c r="E110" s="129"/>
-      <c r="F110" s="131"/>
+      <c r="A110" s="72"/>
+      <c r="B110" s="183"/>
+      <c r="C110" s="72"/>
+      <c r="D110" s="183"/>
+      <c r="E110" s="72"/>
+      <c r="F110" s="74"/>
     </row>
     <row r="111" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="129"/>
-      <c r="B111" s="168"/>
-      <c r="C111" s="129"/>
-      <c r="D111" s="168"/>
-      <c r="E111" s="129"/>
-      <c r="F111" s="131"/>
+      <c r="A111" s="72"/>
+      <c r="B111" s="183"/>
+      <c r="C111" s="72"/>
+      <c r="D111" s="183"/>
+      <c r="E111" s="72"/>
+      <c r="F111" s="74"/>
     </row>
     <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="184"/>
@@ -31168,57 +31168,57 @@
       <c r="F112" s="186"/>
     </row>
     <row r="113" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="165" t="s">
+      <c r="A113" s="167" t="s">
         <v>67</v>
       </c>
-      <c r="B113" s="177"/>
-      <c r="C113" s="177"/>
-      <c r="D113" s="177"/>
-      <c r="E113" s="177"/>
-      <c r="F113" s="178"/>
+      <c r="B113" s="187"/>
+      <c r="C113" s="187"/>
+      <c r="D113" s="187"/>
+      <c r="E113" s="187"/>
+      <c r="F113" s="171"/>
     </row>
     <row r="114" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="165" t="s">
+      <c r="A114" s="167" t="s">
         <v>68</v>
       </c>
-      <c r="B114" s="155"/>
-      <c r="C114" s="156"/>
+      <c r="B114" s="146"/>
+      <c r="C114" s="147"/>
       <c r="D114" s="180">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="E114" s="155"/>
-      <c r="F114" s="156"/>
+      <c r="E114" s="146"/>
+      <c r="F114" s="147"/>
     </row>
     <row r="115" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="181" t="s">
+      <c r="A115" s="172" t="s">
         <v>69</v>
       </c>
-      <c r="B115" s="182"/>
-      <c r="C115" s="170"/>
-      <c r="D115" s="181" t="s">
+      <c r="B115" s="175"/>
+      <c r="C115" s="173"/>
+      <c r="D115" s="172" t="s">
         <v>70</v>
       </c>
-      <c r="E115" s="182"/>
-      <c r="F115" s="170"/>
+      <c r="E115" s="175"/>
+      <c r="F115" s="173"/>
     </row>
     <row r="116" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="B116" s="164">
+      <c r="B116" s="189">
         <f>'DATOS GENERALES'!D30</f>
         <v>0</v>
       </c>
-      <c r="C116" s="164"/>
+      <c r="C116" s="189"/>
       <c r="D116" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="E116" s="164">
+      <c r="E116" s="189">
         <f>'DATOS GENERALES'!L29</f>
         <v>0</v>
       </c>
-      <c r="F116" s="164"/>
+      <c r="F116" s="189"/>
       <c r="G116" s="20">
         <v>0</v>
       </c>
@@ -31227,19 +31227,19 @@
       <c r="A117" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="B117" s="164">
+      <c r="B117" s="189">
         <f>'DATOS GENERALES'!F30</f>
         <v>0</v>
       </c>
-      <c r="C117" s="164"/>
+      <c r="C117" s="189"/>
       <c r="D117" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="E117" s="164">
+      <c r="E117" s="189">
         <f>'DATOS GENERALES'!N29</f>
         <v>0</v>
       </c>
-      <c r="F117" s="164"/>
+      <c r="F117" s="189"/>
       <c r="G117" s="20">
         <v>0</v>
       </c>
@@ -31248,19 +31248,19 @@
       <c r="A118" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="B118" s="164">
+      <c r="B118" s="189">
         <f>'DATOS GENERALES'!H30</f>
         <v>0</v>
       </c>
-      <c r="C118" s="164"/>
+      <c r="C118" s="189"/>
       <c r="D118" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="E118" s="164">
+      <c r="E118" s="189">
         <f>'DATOS GENERALES'!Q29</f>
         <v>0</v>
       </c>
-      <c r="F118" s="164"/>
+      <c r="F118" s="189"/>
       <c r="G118" s="20">
         <v>0</v>
       </c>
@@ -31269,49 +31269,49 @@
       <c r="A119" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="B119" s="164">
+      <c r="B119" s="189">
         <f>'DATOS GENERALES'!D29</f>
         <v>0</v>
       </c>
-      <c r="C119" s="164"/>
+      <c r="C119" s="189"/>
       <c r="D119" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="E119" s="164">
+      <c r="E119" s="189">
         <f>'DATOS GENERALES'!S29</f>
         <v>0</v>
       </c>
-      <c r="F119" s="164"/>
+      <c r="F119" s="189"/>
       <c r="G119" s="20"/>
     </row>
     <row r="120" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="B120" s="164">
+      <c r="B120" s="189">
         <f>'DATOS GENERALES'!F29</f>
         <v>0</v>
       </c>
-      <c r="C120" s="164"/>
+      <c r="C120" s="189"/>
       <c r="D120" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="E120" s="164">
+      <c r="E120" s="189">
         <f>'DATOS GENERALES'!U29</f>
         <v>0</v>
       </c>
-      <c r="F120" s="164"/>
+      <c r="F120" s="189"/>
       <c r="G120" s="20"/>
     </row>
     <row r="121" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="B121" s="164">
+      <c r="B121" s="189">
         <f>'DATOS GENERALES'!H29</f>
         <v>0</v>
       </c>
-      <c r="C121" s="164"/>
+      <c r="C121" s="189"/>
       <c r="D121" s="21"/>
       <c r="E121" s="22"/>
       <c r="F121" s="48"/>
@@ -31321,11 +31321,11 @@
       <c r="A122" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="B122" s="163">
+      <c r="B122" s="195">
         <f>'DATOS GENERALES'!C31</f>
         <v>0</v>
       </c>
-      <c r="C122" s="163"/>
+      <c r="C122" s="195"/>
       <c r="D122" s="43">
         <v>0</v>
       </c>
@@ -31340,46 +31340,46 @@
       </c>
     </row>
     <row r="123" spans="1:7" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="165" t="s">
+      <c r="A123" s="167" t="s">
         <v>58</v>
       </c>
-      <c r="B123" s="133"/>
-      <c r="C123" s="133"/>
-      <c r="D123" s="155"/>
-      <c r="E123" s="155"/>
-      <c r="F123" s="156"/>
+      <c r="B123" s="76"/>
+      <c r="C123" s="76"/>
+      <c r="D123" s="146"/>
+      <c r="E123" s="146"/>
+      <c r="F123" s="147"/>
     </row>
     <row r="124" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="179"/>
-      <c r="B124" s="130"/>
-      <c r="C124" s="130"/>
-      <c r="D124" s="130"/>
-      <c r="E124" s="130"/>
-      <c r="F124" s="131"/>
+      <c r="A124" s="188"/>
+      <c r="B124" s="73"/>
+      <c r="C124" s="73"/>
+      <c r="D124" s="73"/>
+      <c r="E124" s="73"/>
+      <c r="F124" s="74"/>
     </row>
     <row r="125" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="129"/>
-      <c r="B125" s="130"/>
-      <c r="C125" s="130"/>
-      <c r="D125" s="130"/>
-      <c r="E125" s="130"/>
-      <c r="F125" s="131"/>
+      <c r="A125" s="72"/>
+      <c r="B125" s="73"/>
+      <c r="C125" s="73"/>
+      <c r="D125" s="73"/>
+      <c r="E125" s="73"/>
+      <c r="F125" s="74"/>
     </row>
     <row r="126" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="129"/>
-      <c r="B126" s="130"/>
-      <c r="C126" s="130"/>
-      <c r="D126" s="130"/>
-      <c r="E126" s="130"/>
-      <c r="F126" s="131"/>
+      <c r="A126" s="72"/>
+      <c r="B126" s="73"/>
+      <c r="C126" s="73"/>
+      <c r="D126" s="73"/>
+      <c r="E126" s="73"/>
+      <c r="F126" s="74"/>
     </row>
     <row r="127" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="132"/>
-      <c r="B127" s="133"/>
-      <c r="C127" s="133"/>
-      <c r="D127" s="133"/>
-      <c r="E127" s="133"/>
-      <c r="F127" s="134"/>
+      <c r="A127" s="75"/>
+      <c r="B127" s="76"/>
+      <c r="C127" s="76"/>
+      <c r="D127" s="76"/>
+      <c r="E127" s="76"/>
+      <c r="F127" s="77"/>
     </row>
     <row r="128" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="19"/>
@@ -38983,6 +38983,48 @@
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="A58:B74"/>
+    <mergeCell ref="C58:D74"/>
+    <mergeCell ref="E58:F74"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="A40:B56"/>
+    <mergeCell ref="C40:D56"/>
+    <mergeCell ref="E40:F56"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B38"/>
+    <mergeCell ref="C22:D38"/>
+    <mergeCell ref="E22:F38"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A123:F123"/>
+    <mergeCell ref="A124:F127"/>
+    <mergeCell ref="A114:C114"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="E120:F120"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="A95:B112"/>
+    <mergeCell ref="C95:D112"/>
+    <mergeCell ref="E95:F112"/>
     <mergeCell ref="C76:D93"/>
     <mergeCell ref="E76:F93"/>
     <mergeCell ref="B1:E1"/>
@@ -38999,48 +39041,6 @@
     <mergeCell ref="C4:D20"/>
     <mergeCell ref="E4:F20"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="A95:B112"/>
-    <mergeCell ref="C95:D112"/>
-    <mergeCell ref="E95:F112"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A123:F123"/>
-    <mergeCell ref="A124:F127"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="E118:F118"/>
-    <mergeCell ref="E119:F119"/>
-    <mergeCell ref="E120:F120"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B38"/>
-    <mergeCell ref="C22:D38"/>
-    <mergeCell ref="E22:F38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="A40:B56"/>
-    <mergeCell ref="C40:D56"/>
-    <mergeCell ref="E40:F56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="A58:B74"/>
-    <mergeCell ref="C58:D74"/>
-    <mergeCell ref="E58:F74"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="E121" xr:uid="{A8391F7A-9A26-42E9-A6BB-AC7965E438D5}"/>
@@ -39070,934 +39070,934 @@
   <sheetData>
     <row r="1" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9"/>
-      <c r="B1" s="189" t="s">
+      <c r="B1" s="166" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
       <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="167" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="165">
-        <f>'MEDICIONES DE ENTRADA '!C2</f>
+      <c r="B2" s="168"/>
+      <c r="C2" s="167">
+        <f>'MEDICIONES DE ENTRADA'!C2</f>
         <v>0</v>
       </c>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="156"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="147"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="165" t="s">
+      <c r="A3" s="167" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="166"/>
+      <c r="B3" s="179"/>
       <c r="C3" s="180" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="212"/>
-      <c r="E3" s="213" t="s">
+      <c r="D3" s="196"/>
+      <c r="E3" s="197" t="s">
         <v>134</v>
       </c>
-      <c r="F3" s="166"/>
+      <c r="F3" s="179"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="169"/>
-      <c r="B4" s="170"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="170"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="170"/>
+      <c r="A4" s="177"/>
+      <c r="B4" s="173"/>
+      <c r="C4" s="177"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="177"/>
+      <c r="F4" s="173"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="129"/>
-      <c r="B5" s="131"/>
-      <c r="C5" s="129"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="131"/>
+      <c r="A5" s="72"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="74"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="129"/>
-      <c r="B6" s="131"/>
-      <c r="C6" s="129"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="131"/>
+      <c r="A6" s="72"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="74"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="129"/>
-      <c r="B7" s="131"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="131"/>
+      <c r="A7" s="72"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="74"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="129"/>
-      <c r="B8" s="131"/>
-      <c r="C8" s="129"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="129"/>
-      <c r="F8" s="131"/>
+      <c r="A8" s="72"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="74"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="129"/>
-      <c r="B9" s="131"/>
-      <c r="C9" s="129"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="131"/>
+      <c r="A9" s="72"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="74"/>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="129"/>
-      <c r="B10" s="131"/>
-      <c r="C10" s="129"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="129"/>
-      <c r="F10" s="131"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="74"/>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="129"/>
-      <c r="B11" s="131"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="131"/>
+      <c r="A11" s="72"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="74"/>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="129"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="131"/>
+      <c r="A12" s="72"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="74"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="129"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="129"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="129"/>
-      <c r="F13" s="131"/>
+      <c r="A13" s="72"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="74"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="129"/>
-      <c r="B14" s="131"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="131"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="74"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="129"/>
-      <c r="B15" s="131"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="131"/>
+      <c r="A15" s="72"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="74"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="129"/>
-      <c r="B16" s="131"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="131"/>
+      <c r="A16" s="72"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="74"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="129"/>
-      <c r="B17" s="131"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="131"/>
+      <c r="A17" s="72"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="74"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="129"/>
-      <c r="B18" s="131"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="131"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="131"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="74"/>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="129"/>
-      <c r="B19" s="131"/>
-      <c r="C19" s="129"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="131"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="74"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="132"/>
-      <c r="B20" s="134"/>
-      <c r="C20" s="132"/>
-      <c r="D20" s="134"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="134"/>
+      <c r="A20" s="75"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="77"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="171" t="s">
+      <c r="A21" s="178" t="s">
         <v>135</v>
       </c>
-      <c r="B21" s="166"/>
-      <c r="C21" s="171" t="s">
+      <c r="B21" s="179"/>
+      <c r="C21" s="178" t="s">
         <v>136</v>
       </c>
-      <c r="D21" s="166"/>
-      <c r="E21" s="171" t="s">
+      <c r="D21" s="179"/>
+      <c r="E21" s="178" t="s">
         <v>137</v>
       </c>
-      <c r="F21" s="166"/>
+      <c r="F21" s="179"/>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="169"/>
-      <c r="B22" s="170"/>
-      <c r="C22" s="169"/>
-      <c r="D22" s="170"/>
-      <c r="E22" s="169"/>
-      <c r="F22" s="170"/>
+      <c r="A22" s="177"/>
+      <c r="B22" s="173"/>
+      <c r="C22" s="177"/>
+      <c r="D22" s="173"/>
+      <c r="E22" s="177"/>
+      <c r="F22" s="173"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="129"/>
-      <c r="B23" s="131"/>
-      <c r="C23" s="129"/>
-      <c r="D23" s="131"/>
-      <c r="E23" s="129"/>
-      <c r="F23" s="131"/>
+      <c r="A23" s="72"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="72"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="74"/>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="129"/>
-      <c r="B24" s="131"/>
-      <c r="C24" s="129"/>
-      <c r="D24" s="131"/>
-      <c r="E24" s="129"/>
-      <c r="F24" s="131"/>
+      <c r="A24" s="72"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="74"/>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="129"/>
-      <c r="B25" s="131"/>
-      <c r="C25" s="129"/>
-      <c r="D25" s="131"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="131"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="74"/>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="129"/>
-      <c r="B26" s="131"/>
-      <c r="C26" s="129"/>
-      <c r="D26" s="131"/>
-      <c r="E26" s="129"/>
-      <c r="F26" s="131"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="72"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="74"/>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="129"/>
-      <c r="B27" s="131"/>
-      <c r="C27" s="129"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="131"/>
+      <c r="A27" s="72"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="74"/>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="129"/>
-      <c r="B28" s="131"/>
-      <c r="C28" s="129"/>
-      <c r="D28" s="131"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="131"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="74"/>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="129"/>
-      <c r="B29" s="131"/>
-      <c r="C29" s="129"/>
-      <c r="D29" s="131"/>
-      <c r="E29" s="129"/>
-      <c r="F29" s="131"/>
+      <c r="A29" s="72"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="74"/>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="129"/>
-      <c r="B30" s="131"/>
-      <c r="C30" s="129"/>
-      <c r="D30" s="131"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="131"/>
+      <c r="A30" s="72"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="74"/>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="129"/>
-      <c r="B31" s="131"/>
-      <c r="C31" s="129"/>
-      <c r="D31" s="131"/>
-      <c r="E31" s="129"/>
-      <c r="F31" s="131"/>
+      <c r="A31" s="72"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="74"/>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="129"/>
-      <c r="B32" s="131"/>
-      <c r="C32" s="129"/>
-      <c r="D32" s="131"/>
-      <c r="E32" s="129"/>
-      <c r="F32" s="131"/>
+      <c r="A32" s="72"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="74"/>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="129"/>
-      <c r="B33" s="131"/>
-      <c r="C33" s="129"/>
-      <c r="D33" s="131"/>
-      <c r="E33" s="129"/>
-      <c r="F33" s="131"/>
+      <c r="A33" s="72"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="74"/>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="129"/>
-      <c r="B34" s="131"/>
-      <c r="C34" s="129"/>
-      <c r="D34" s="131"/>
-      <c r="E34" s="129"/>
-      <c r="F34" s="131"/>
+      <c r="A34" s="72"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="74"/>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="129"/>
-      <c r="B35" s="131"/>
-      <c r="C35" s="129"/>
-      <c r="D35" s="131"/>
-      <c r="E35" s="129"/>
-      <c r="F35" s="131"/>
+      <c r="A35" s="72"/>
+      <c r="B35" s="74"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="74"/>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="129"/>
-      <c r="B36" s="131"/>
-      <c r="C36" s="129"/>
-      <c r="D36" s="131"/>
-      <c r="E36" s="129"/>
-      <c r="F36" s="131"/>
+      <c r="A36" s="72"/>
+      <c r="B36" s="74"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="74"/>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="129"/>
-      <c r="B37" s="131"/>
-      <c r="C37" s="129"/>
-      <c r="D37" s="131"/>
-      <c r="E37" s="129"/>
-      <c r="F37" s="131"/>
+      <c r="A37" s="72"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="74"/>
     </row>
     <row r="38" spans="1:6" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="132"/>
-      <c r="B38" s="134"/>
-      <c r="C38" s="132"/>
-      <c r="D38" s="134"/>
-      <c r="E38" s="132"/>
-      <c r="F38" s="134"/>
+      <c r="A38" s="75"/>
+      <c r="B38" s="77"/>
+      <c r="C38" s="75"/>
+      <c r="D38" s="77"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="77"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="171" t="s">
+      <c r="A39" s="178" t="s">
         <v>138</v>
       </c>
-      <c r="B39" s="166"/>
-      <c r="C39" s="171" t="s">
+      <c r="B39" s="179"/>
+      <c r="C39" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="166"/>
-      <c r="E39" s="171" t="s">
+      <c r="D39" s="179"/>
+      <c r="E39" s="178" t="s">
         <v>139</v>
       </c>
-      <c r="F39" s="166"/>
+      <c r="F39" s="179"/>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="169"/>
-      <c r="B40" s="170"/>
-      <c r="C40" s="169"/>
-      <c r="D40" s="170"/>
-      <c r="E40" s="169"/>
-      <c r="F40" s="170"/>
+      <c r="A40" s="177"/>
+      <c r="B40" s="173"/>
+      <c r="C40" s="177"/>
+      <c r="D40" s="173"/>
+      <c r="E40" s="177"/>
+      <c r="F40" s="173"/>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="129"/>
-      <c r="B41" s="131"/>
-      <c r="C41" s="129"/>
-      <c r="D41" s="131"/>
-      <c r="E41" s="129"/>
-      <c r="F41" s="131"/>
+      <c r="A41" s="72"/>
+      <c r="B41" s="74"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="74"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="74"/>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="129"/>
-      <c r="B42" s="131"/>
-      <c r="C42" s="129"/>
-      <c r="D42" s="131"/>
-      <c r="E42" s="129"/>
-      <c r="F42" s="131"/>
+      <c r="A42" s="72"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="74"/>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="129"/>
-      <c r="B43" s="131"/>
-      <c r="C43" s="129"/>
-      <c r="D43" s="131"/>
-      <c r="E43" s="129"/>
-      <c r="F43" s="131"/>
+      <c r="A43" s="72"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="74"/>
+      <c r="E43" s="72"/>
+      <c r="F43" s="74"/>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="129"/>
-      <c r="B44" s="131"/>
-      <c r="C44" s="129"/>
-      <c r="D44" s="131"/>
-      <c r="E44" s="129"/>
-      <c r="F44" s="131"/>
+      <c r="A44" s="72"/>
+      <c r="B44" s="74"/>
+      <c r="C44" s="72"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="72"/>
+      <c r="F44" s="74"/>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="129"/>
-      <c r="B45" s="131"/>
-      <c r="C45" s="129"/>
-      <c r="D45" s="131"/>
-      <c r="E45" s="129"/>
-      <c r="F45" s="131"/>
+      <c r="A45" s="72"/>
+      <c r="B45" s="74"/>
+      <c r="C45" s="72"/>
+      <c r="D45" s="74"/>
+      <c r="E45" s="72"/>
+      <c r="F45" s="74"/>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="129"/>
-      <c r="B46" s="131"/>
-      <c r="C46" s="129"/>
-      <c r="D46" s="131"/>
-      <c r="E46" s="129"/>
-      <c r="F46" s="131"/>
+      <c r="A46" s="72"/>
+      <c r="B46" s="74"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="74"/>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="129"/>
-      <c r="B47" s="131"/>
-      <c r="C47" s="129"/>
-      <c r="D47" s="131"/>
-      <c r="E47" s="129"/>
-      <c r="F47" s="131"/>
+      <c r="A47" s="72"/>
+      <c r="B47" s="74"/>
+      <c r="C47" s="72"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="72"/>
+      <c r="F47" s="74"/>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="129"/>
-      <c r="B48" s="131"/>
-      <c r="C48" s="129"/>
-      <c r="D48" s="131"/>
-      <c r="E48" s="129"/>
-      <c r="F48" s="131"/>
+      <c r="A48" s="72"/>
+      <c r="B48" s="74"/>
+      <c r="C48" s="72"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="72"/>
+      <c r="F48" s="74"/>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="129"/>
-      <c r="B49" s="131"/>
-      <c r="C49" s="129"/>
-      <c r="D49" s="131"/>
-      <c r="E49" s="129"/>
-      <c r="F49" s="131"/>
+      <c r="A49" s="72"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="72"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="74"/>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="129"/>
-      <c r="B50" s="131"/>
-      <c r="C50" s="129"/>
-      <c r="D50" s="131"/>
-      <c r="E50" s="129"/>
-      <c r="F50" s="131"/>
+      <c r="A50" s="72"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="72"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="72"/>
+      <c r="F50" s="74"/>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="129"/>
-      <c r="B51" s="131"/>
-      <c r="C51" s="129"/>
-      <c r="D51" s="131"/>
-      <c r="E51" s="129"/>
-      <c r="F51" s="131"/>
+      <c r="A51" s="72"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="72"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="72"/>
+      <c r="F51" s="74"/>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="129"/>
-      <c r="B52" s="131"/>
-      <c r="C52" s="129"/>
-      <c r="D52" s="131"/>
-      <c r="E52" s="129"/>
-      <c r="F52" s="131"/>
+      <c r="A52" s="72"/>
+      <c r="B52" s="74"/>
+      <c r="C52" s="72"/>
+      <c r="D52" s="74"/>
+      <c r="E52" s="72"/>
+      <c r="F52" s="74"/>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="129"/>
-      <c r="B53" s="131"/>
-      <c r="C53" s="129"/>
-      <c r="D53" s="131"/>
-      <c r="E53" s="129"/>
-      <c r="F53" s="131"/>
+      <c r="A53" s="72"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="74"/>
+      <c r="E53" s="72"/>
+      <c r="F53" s="74"/>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="129"/>
-      <c r="B54" s="131"/>
-      <c r="C54" s="129"/>
-      <c r="D54" s="131"/>
-      <c r="E54" s="129"/>
-      <c r="F54" s="131"/>
+      <c r="A54" s="72"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="72"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="72"/>
+      <c r="F54" s="74"/>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="129"/>
-      <c r="B55" s="131"/>
-      <c r="C55" s="129"/>
-      <c r="D55" s="131"/>
-      <c r="E55" s="129"/>
-      <c r="F55" s="131"/>
+      <c r="A55" s="72"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="72"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="72"/>
+      <c r="F55" s="74"/>
     </row>
     <row r="56" spans="1:6" ht="19.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="129"/>
-      <c r="B56" s="131"/>
-      <c r="C56" s="129"/>
-      <c r="D56" s="131"/>
-      <c r="E56" s="129"/>
-      <c r="F56" s="131"/>
+      <c r="A56" s="72"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="72"/>
+      <c r="D56" s="74"/>
+      <c r="E56" s="72"/>
+      <c r="F56" s="74"/>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="165" t="s">
+      <c r="A57" s="167" t="s">
         <v>140</v>
       </c>
-      <c r="B57" s="166"/>
-      <c r="C57" s="165" t="s">
+      <c r="B57" s="179"/>
+      <c r="C57" s="167" t="s">
         <v>65</v>
       </c>
-      <c r="D57" s="166"/>
-      <c r="E57" s="165" t="s">
+      <c r="D57" s="179"/>
+      <c r="E57" s="167" t="s">
         <v>66</v>
       </c>
-      <c r="F57" s="166"/>
+      <c r="F57" s="179"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="169"/>
-      <c r="B58" s="170"/>
-      <c r="C58" s="169"/>
-      <c r="D58" s="170"/>
-      <c r="E58" s="169"/>
-      <c r="F58" s="170"/>
+      <c r="A58" s="177"/>
+      <c r="B58" s="173"/>
+      <c r="C58" s="177"/>
+      <c r="D58" s="173"/>
+      <c r="E58" s="177"/>
+      <c r="F58" s="173"/>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="129"/>
-      <c r="B59" s="131"/>
-      <c r="C59" s="129"/>
-      <c r="D59" s="131"/>
-      <c r="E59" s="129"/>
-      <c r="F59" s="131"/>
+      <c r="A59" s="72"/>
+      <c r="B59" s="74"/>
+      <c r="C59" s="72"/>
+      <c r="D59" s="74"/>
+      <c r="E59" s="72"/>
+      <c r="F59" s="74"/>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="129"/>
-      <c r="B60" s="131"/>
-      <c r="C60" s="129"/>
-      <c r="D60" s="131"/>
-      <c r="E60" s="129"/>
-      <c r="F60" s="131"/>
+      <c r="A60" s="72"/>
+      <c r="B60" s="74"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="74"/>
+      <c r="E60" s="72"/>
+      <c r="F60" s="74"/>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="129"/>
-      <c r="B61" s="131"/>
-      <c r="C61" s="129"/>
-      <c r="D61" s="131"/>
-      <c r="E61" s="129"/>
-      <c r="F61" s="131"/>
+      <c r="A61" s="72"/>
+      <c r="B61" s="74"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="74"/>
+      <c r="E61" s="72"/>
+      <c r="F61" s="74"/>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="129"/>
-      <c r="B62" s="131"/>
-      <c r="C62" s="129"/>
-      <c r="D62" s="131"/>
-      <c r="E62" s="129"/>
-      <c r="F62" s="131"/>
+      <c r="A62" s="72"/>
+      <c r="B62" s="74"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="74"/>
+      <c r="E62" s="72"/>
+      <c r="F62" s="74"/>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="129"/>
-      <c r="B63" s="131"/>
-      <c r="C63" s="129"/>
-      <c r="D63" s="131"/>
-      <c r="E63" s="129"/>
-      <c r="F63" s="131"/>
+      <c r="A63" s="72"/>
+      <c r="B63" s="74"/>
+      <c r="C63" s="72"/>
+      <c r="D63" s="74"/>
+      <c r="E63" s="72"/>
+      <c r="F63" s="74"/>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="129"/>
-      <c r="B64" s="131"/>
-      <c r="C64" s="129"/>
-      <c r="D64" s="131"/>
-      <c r="E64" s="129"/>
-      <c r="F64" s="131"/>
+      <c r="A64" s="72"/>
+      <c r="B64" s="74"/>
+      <c r="C64" s="72"/>
+      <c r="D64" s="74"/>
+      <c r="E64" s="72"/>
+      <c r="F64" s="74"/>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="129"/>
-      <c r="B65" s="131"/>
-      <c r="C65" s="129"/>
-      <c r="D65" s="131"/>
-      <c r="E65" s="129"/>
-      <c r="F65" s="131"/>
+      <c r="A65" s="72"/>
+      <c r="B65" s="74"/>
+      <c r="C65" s="72"/>
+      <c r="D65" s="74"/>
+      <c r="E65" s="72"/>
+      <c r="F65" s="74"/>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="129"/>
-      <c r="B66" s="131"/>
-      <c r="C66" s="129"/>
-      <c r="D66" s="131"/>
-      <c r="E66" s="129"/>
-      <c r="F66" s="131"/>
+      <c r="A66" s="72"/>
+      <c r="B66" s="74"/>
+      <c r="C66" s="72"/>
+      <c r="D66" s="74"/>
+      <c r="E66" s="72"/>
+      <c r="F66" s="74"/>
     </row>
     <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="129"/>
-      <c r="B67" s="131"/>
-      <c r="C67" s="129"/>
-      <c r="D67" s="131"/>
-      <c r="E67" s="129"/>
-      <c r="F67" s="131"/>
+      <c r="A67" s="72"/>
+      <c r="B67" s="74"/>
+      <c r="C67" s="72"/>
+      <c r="D67" s="74"/>
+      <c r="E67" s="72"/>
+      <c r="F67" s="74"/>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="129"/>
-      <c r="B68" s="131"/>
-      <c r="C68" s="129"/>
-      <c r="D68" s="131"/>
-      <c r="E68" s="129"/>
-      <c r="F68" s="131"/>
+      <c r="A68" s="72"/>
+      <c r="B68" s="74"/>
+      <c r="C68" s="72"/>
+      <c r="D68" s="74"/>
+      <c r="E68" s="72"/>
+      <c r="F68" s="74"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="129"/>
-      <c r="B69" s="131"/>
-      <c r="C69" s="129"/>
-      <c r="D69" s="131"/>
-      <c r="E69" s="129"/>
-      <c r="F69" s="131"/>
+      <c r="A69" s="72"/>
+      <c r="B69" s="74"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="74"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="74"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="129"/>
-      <c r="B70" s="131"/>
-      <c r="C70" s="129"/>
-      <c r="D70" s="131"/>
-      <c r="E70" s="129"/>
-      <c r="F70" s="131"/>
+      <c r="A70" s="72"/>
+      <c r="B70" s="74"/>
+      <c r="C70" s="72"/>
+      <c r="D70" s="74"/>
+      <c r="E70" s="72"/>
+      <c r="F70" s="74"/>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="129"/>
-      <c r="B71" s="131"/>
-      <c r="C71" s="129"/>
-      <c r="D71" s="131"/>
-      <c r="E71" s="129"/>
-      <c r="F71" s="131"/>
+      <c r="A71" s="72"/>
+      <c r="B71" s="74"/>
+      <c r="C71" s="72"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="72"/>
+      <c r="F71" s="74"/>
     </row>
     <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="129"/>
-      <c r="B72" s="131"/>
-      <c r="C72" s="129"/>
-      <c r="D72" s="131"/>
-      <c r="E72" s="129"/>
-      <c r="F72" s="131"/>
+      <c r="A72" s="72"/>
+      <c r="B72" s="74"/>
+      <c r="C72" s="72"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="72"/>
+      <c r="F72" s="74"/>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="129"/>
-      <c r="B73" s="131"/>
-      <c r="C73" s="129"/>
-      <c r="D73" s="131"/>
-      <c r="E73" s="129"/>
-      <c r="F73" s="131"/>
+      <c r="A73" s="72"/>
+      <c r="B73" s="74"/>
+      <c r="C73" s="72"/>
+      <c r="D73" s="74"/>
+      <c r="E73" s="72"/>
+      <c r="F73" s="74"/>
     </row>
     <row r="74" spans="1:6" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="129"/>
-      <c r="B74" s="131"/>
-      <c r="C74" s="129"/>
-      <c r="D74" s="131"/>
-      <c r="E74" s="129"/>
-      <c r="F74" s="131"/>
+      <c r="A74" s="72"/>
+      <c r="B74" s="74"/>
+      <c r="C74" s="72"/>
+      <c r="D74" s="74"/>
+      <c r="E74" s="72"/>
+      <c r="F74" s="74"/>
     </row>
     <row r="75" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="165" t="s">
+      <c r="A75" s="167" t="s">
         <v>61</v>
       </c>
-      <c r="B75" s="191"/>
-      <c r="C75" s="165" t="s">
+      <c r="B75" s="169"/>
+      <c r="C75" s="167" t="s">
         <v>62</v>
       </c>
-      <c r="D75" s="192"/>
-      <c r="E75" s="165" t="s">
+      <c r="D75" s="170"/>
+      <c r="E75" s="167" t="s">
         <v>74</v>
       </c>
-      <c r="F75" s="178"/>
+      <c r="F75" s="171"/>
     </row>
     <row r="76" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="187"/>
-      <c r="B76" s="128"/>
-      <c r="C76" s="187"/>
-      <c r="D76" s="128"/>
-      <c r="E76" s="188"/>
-      <c r="F76" s="128"/>
+      <c r="A76" s="164"/>
+      <c r="B76" s="71"/>
+      <c r="C76" s="164"/>
+      <c r="D76" s="71"/>
+      <c r="E76" s="165"/>
+      <c r="F76" s="71"/>
     </row>
     <row r="77" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="129"/>
-      <c r="B77" s="131"/>
-      <c r="C77" s="129"/>
-      <c r="D77" s="131"/>
-      <c r="E77" s="130"/>
-      <c r="F77" s="131"/>
+      <c r="A77" s="72"/>
+      <c r="B77" s="74"/>
+      <c r="C77" s="72"/>
+      <c r="D77" s="74"/>
+      <c r="E77" s="73"/>
+      <c r="F77" s="74"/>
     </row>
     <row r="78" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="129"/>
-      <c r="B78" s="131"/>
-      <c r="C78" s="129"/>
-      <c r="D78" s="131"/>
-      <c r="E78" s="130"/>
-      <c r="F78" s="131"/>
+      <c r="A78" s="72"/>
+      <c r="B78" s="74"/>
+      <c r="C78" s="72"/>
+      <c r="D78" s="74"/>
+      <c r="E78" s="73"/>
+      <c r="F78" s="74"/>
     </row>
     <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="129"/>
-      <c r="B79" s="131"/>
-      <c r="C79" s="129"/>
-      <c r="D79" s="131"/>
-      <c r="E79" s="130"/>
-      <c r="F79" s="131"/>
+      <c r="A79" s="72"/>
+      <c r="B79" s="74"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="74"/>
+      <c r="E79" s="73"/>
+      <c r="F79" s="74"/>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="129"/>
-      <c r="B80" s="131"/>
-      <c r="C80" s="129"/>
-      <c r="D80" s="131"/>
-      <c r="E80" s="130"/>
-      <c r="F80" s="131"/>
+      <c r="A80" s="72"/>
+      <c r="B80" s="74"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="74"/>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="129"/>
-      <c r="B81" s="131"/>
-      <c r="C81" s="129"/>
-      <c r="D81" s="131"/>
-      <c r="E81" s="130"/>
-      <c r="F81" s="131"/>
+      <c r="A81" s="72"/>
+      <c r="B81" s="74"/>
+      <c r="C81" s="72"/>
+      <c r="D81" s="74"/>
+      <c r="E81" s="73"/>
+      <c r="F81" s="74"/>
     </row>
     <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="129"/>
-      <c r="B82" s="131"/>
-      <c r="C82" s="129"/>
-      <c r="D82" s="131"/>
-      <c r="E82" s="130"/>
-      <c r="F82" s="131"/>
+      <c r="A82" s="72"/>
+      <c r="B82" s="74"/>
+      <c r="C82" s="72"/>
+      <c r="D82" s="74"/>
+      <c r="E82" s="73"/>
+      <c r="F82" s="74"/>
     </row>
     <row r="83" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="129"/>
-      <c r="B83" s="131"/>
-      <c r="C83" s="129"/>
-      <c r="D83" s="131"/>
-      <c r="E83" s="130"/>
-      <c r="F83" s="131"/>
+      <c r="A83" s="72"/>
+      <c r="B83" s="74"/>
+      <c r="C83" s="72"/>
+      <c r="D83" s="74"/>
+      <c r="E83" s="73"/>
+      <c r="F83" s="74"/>
     </row>
     <row r="84" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="129"/>
-      <c r="B84" s="131"/>
-      <c r="C84" s="129"/>
-      <c r="D84" s="131"/>
-      <c r="E84" s="130"/>
-      <c r="F84" s="131"/>
+      <c r="A84" s="72"/>
+      <c r="B84" s="74"/>
+      <c r="C84" s="72"/>
+      <c r="D84" s="74"/>
+      <c r="E84" s="73"/>
+      <c r="F84" s="74"/>
     </row>
     <row r="85" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="129"/>
-      <c r="B85" s="131"/>
-      <c r="C85" s="129"/>
-      <c r="D85" s="131"/>
-      <c r="E85" s="130"/>
-      <c r="F85" s="131"/>
+      <c r="A85" s="72"/>
+      <c r="B85" s="74"/>
+      <c r="C85" s="72"/>
+      <c r="D85" s="74"/>
+      <c r="E85" s="73"/>
+      <c r="F85" s="74"/>
     </row>
     <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="129"/>
-      <c r="B86" s="131"/>
-      <c r="C86" s="129"/>
-      <c r="D86" s="131"/>
-      <c r="E86" s="130"/>
-      <c r="F86" s="131"/>
+      <c r="A86" s="72"/>
+      <c r="B86" s="74"/>
+      <c r="C86" s="72"/>
+      <c r="D86" s="74"/>
+      <c r="E86" s="73"/>
+      <c r="F86" s="74"/>
     </row>
     <row r="87" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="129"/>
-      <c r="B87" s="131"/>
-      <c r="C87" s="129"/>
-      <c r="D87" s="131"/>
-      <c r="E87" s="130"/>
-      <c r="F87" s="131"/>
+      <c r="A87" s="72"/>
+      <c r="B87" s="74"/>
+      <c r="C87" s="72"/>
+      <c r="D87" s="74"/>
+      <c r="E87" s="73"/>
+      <c r="F87" s="74"/>
     </row>
     <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="129"/>
-      <c r="B88" s="131"/>
-      <c r="C88" s="129"/>
-      <c r="D88" s="131"/>
-      <c r="E88" s="130"/>
-      <c r="F88" s="131"/>
+      <c r="A88" s="72"/>
+      <c r="B88" s="74"/>
+      <c r="C88" s="72"/>
+      <c r="D88" s="74"/>
+      <c r="E88" s="73"/>
+      <c r="F88" s="74"/>
     </row>
     <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="129"/>
-      <c r="B89" s="131"/>
-      <c r="C89" s="129"/>
-      <c r="D89" s="131"/>
-      <c r="E89" s="130"/>
-      <c r="F89" s="131"/>
+      <c r="A89" s="72"/>
+      <c r="B89" s="74"/>
+      <c r="C89" s="72"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="73"/>
+      <c r="F89" s="74"/>
     </row>
     <row r="90" spans="1:6" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="129"/>
-      <c r="B90" s="131"/>
-      <c r="C90" s="129"/>
-      <c r="D90" s="131"/>
-      <c r="E90" s="130"/>
-      <c r="F90" s="131"/>
+      <c r="A90" s="72"/>
+      <c r="B90" s="74"/>
+      <c r="C90" s="72"/>
+      <c r="D90" s="74"/>
+      <c r="E90" s="73"/>
+      <c r="F90" s="74"/>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="129"/>
-      <c r="B91" s="131"/>
-      <c r="C91" s="129"/>
-      <c r="D91" s="131"/>
-      <c r="E91" s="130"/>
-      <c r="F91" s="131"/>
+      <c r="A91" s="72"/>
+      <c r="B91" s="74"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="74"/>
+      <c r="E91" s="73"/>
+      <c r="F91" s="74"/>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="129"/>
-      <c r="B92" s="131"/>
-      <c r="C92" s="129"/>
-      <c r="D92" s="131"/>
-      <c r="E92" s="130"/>
-      <c r="F92" s="131"/>
+      <c r="A92" s="72"/>
+      <c r="B92" s="74"/>
+      <c r="C92" s="72"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="73"/>
+      <c r="F92" s="74"/>
     </row>
     <row r="93" spans="1:6" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="132"/>
-      <c r="B93" s="134"/>
-      <c r="C93" s="132"/>
-      <c r="D93" s="134"/>
-      <c r="E93" s="133"/>
-      <c r="F93" s="134"/>
+      <c r="A93" s="75"/>
+      <c r="B93" s="77"/>
+      <c r="C93" s="75"/>
+      <c r="D93" s="77"/>
+      <c r="E93" s="76"/>
+      <c r="F93" s="77"/>
     </row>
     <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="165" t="s">
+      <c r="A94" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="B94" s="192"/>
-      <c r="C94" s="183" t="s">
+      <c r="B94" s="170"/>
+      <c r="C94" s="181" t="s">
         <v>65</v>
       </c>
-      <c r="D94" s="178"/>
-      <c r="E94" s="183" t="s">
+      <c r="D94" s="171"/>
+      <c r="E94" s="181" t="s">
         <v>66</v>
       </c>
-      <c r="F94" s="178"/>
+      <c r="F94" s="171"/>
     </row>
     <row r="95" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="167"/>
-      <c r="B95" s="168"/>
-      <c r="C95" s="167"/>
-      <c r="D95" s="168"/>
-      <c r="E95" s="167"/>
-      <c r="F95" s="131"/>
+      <c r="A95" s="182"/>
+      <c r="B95" s="183"/>
+      <c r="C95" s="182"/>
+      <c r="D95" s="183"/>
+      <c r="E95" s="182"/>
+      <c r="F95" s="74"/>
     </row>
     <row r="96" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="129"/>
-      <c r="B96" s="168"/>
-      <c r="C96" s="129"/>
-      <c r="D96" s="168"/>
-      <c r="E96" s="129"/>
-      <c r="F96" s="131"/>
+      <c r="A96" s="72"/>
+      <c r="B96" s="183"/>
+      <c r="C96" s="72"/>
+      <c r="D96" s="183"/>
+      <c r="E96" s="72"/>
+      <c r="F96" s="74"/>
     </row>
     <row r="97" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="129"/>
-      <c r="B97" s="168"/>
-      <c r="C97" s="129"/>
-      <c r="D97" s="168"/>
-      <c r="E97" s="129"/>
-      <c r="F97" s="131"/>
+      <c r="A97" s="72"/>
+      <c r="B97" s="183"/>
+      <c r="C97" s="72"/>
+      <c r="D97" s="183"/>
+      <c r="E97" s="72"/>
+      <c r="F97" s="74"/>
     </row>
     <row r="98" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="129"/>
-      <c r="B98" s="168"/>
-      <c r="C98" s="129"/>
-      <c r="D98" s="168"/>
-      <c r="E98" s="129"/>
-      <c r="F98" s="131"/>
+      <c r="A98" s="72"/>
+      <c r="B98" s="183"/>
+      <c r="C98" s="72"/>
+      <c r="D98" s="183"/>
+      <c r="E98" s="72"/>
+      <c r="F98" s="74"/>
     </row>
     <row r="99" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="129"/>
-      <c r="B99" s="168"/>
-      <c r="C99" s="129"/>
-      <c r="D99" s="168"/>
-      <c r="E99" s="129"/>
-      <c r="F99" s="131"/>
+      <c r="A99" s="72"/>
+      <c r="B99" s="183"/>
+      <c r="C99" s="72"/>
+      <c r="D99" s="183"/>
+      <c r="E99" s="72"/>
+      <c r="F99" s="74"/>
     </row>
     <row r="100" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="129"/>
-      <c r="B100" s="168"/>
-      <c r="C100" s="129"/>
-      <c r="D100" s="168"/>
-      <c r="E100" s="129"/>
-      <c r="F100" s="131"/>
+      <c r="A100" s="72"/>
+      <c r="B100" s="183"/>
+      <c r="C100" s="72"/>
+      <c r="D100" s="183"/>
+      <c r="E100" s="72"/>
+      <c r="F100" s="74"/>
     </row>
     <row r="101" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="129"/>
-      <c r="B101" s="168"/>
-      <c r="C101" s="129"/>
-      <c r="D101" s="168"/>
-      <c r="E101" s="129"/>
-      <c r="F101" s="131"/>
+      <c r="A101" s="72"/>
+      <c r="B101" s="183"/>
+      <c r="C101" s="72"/>
+      <c r="D101" s="183"/>
+      <c r="E101" s="72"/>
+      <c r="F101" s="74"/>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="129"/>
-      <c r="B102" s="168"/>
-      <c r="C102" s="129"/>
-      <c r="D102" s="168"/>
-      <c r="E102" s="129"/>
-      <c r="F102" s="131"/>
+      <c r="A102" s="72"/>
+      <c r="B102" s="183"/>
+      <c r="C102" s="72"/>
+      <c r="D102" s="183"/>
+      <c r="E102" s="72"/>
+      <c r="F102" s="74"/>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="129"/>
-      <c r="B103" s="168"/>
-      <c r="C103" s="129"/>
-      <c r="D103" s="168"/>
-      <c r="E103" s="129"/>
-      <c r="F103" s="131"/>
+      <c r="A103" s="72"/>
+      <c r="B103" s="183"/>
+      <c r="C103" s="72"/>
+      <c r="D103" s="183"/>
+      <c r="E103" s="72"/>
+      <c r="F103" s="74"/>
     </row>
     <row r="104" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="129"/>
-      <c r="B104" s="168"/>
-      <c r="C104" s="129"/>
-      <c r="D104" s="168"/>
-      <c r="E104" s="129"/>
-      <c r="F104" s="131"/>
+      <c r="A104" s="72"/>
+      <c r="B104" s="183"/>
+      <c r="C104" s="72"/>
+      <c r="D104" s="183"/>
+      <c r="E104" s="72"/>
+      <c r="F104" s="74"/>
     </row>
     <row r="105" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="129"/>
-      <c r="B105" s="168"/>
-      <c r="C105" s="129"/>
-      <c r="D105" s="168"/>
-      <c r="E105" s="129"/>
-      <c r="F105" s="131"/>
+      <c r="A105" s="72"/>
+      <c r="B105" s="183"/>
+      <c r="C105" s="72"/>
+      <c r="D105" s="183"/>
+      <c r="E105" s="72"/>
+      <c r="F105" s="74"/>
     </row>
     <row r="106" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="129"/>
-      <c r="B106" s="168"/>
-      <c r="C106" s="129"/>
-      <c r="D106" s="168"/>
-      <c r="E106" s="129"/>
-      <c r="F106" s="131"/>
+      <c r="A106" s="72"/>
+      <c r="B106" s="183"/>
+      <c r="C106" s="72"/>
+      <c r="D106" s="183"/>
+      <c r="E106" s="72"/>
+      <c r="F106" s="74"/>
     </row>
     <row r="107" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="129"/>
-      <c r="B107" s="168"/>
-      <c r="C107" s="129"/>
-      <c r="D107" s="168"/>
-      <c r="E107" s="129"/>
-      <c r="F107" s="131"/>
+      <c r="A107" s="72"/>
+      <c r="B107" s="183"/>
+      <c r="C107" s="72"/>
+      <c r="D107" s="183"/>
+      <c r="E107" s="72"/>
+      <c r="F107" s="74"/>
     </row>
     <row r="108" spans="1:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="129"/>
-      <c r="B108" s="168"/>
-      <c r="C108" s="129"/>
-      <c r="D108" s="168"/>
-      <c r="E108" s="129"/>
-      <c r="F108" s="131"/>
+      <c r="A108" s="72"/>
+      <c r="B108" s="183"/>
+      <c r="C108" s="72"/>
+      <c r="D108" s="183"/>
+      <c r="E108" s="72"/>
+      <c r="F108" s="74"/>
     </row>
     <row r="109" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="129"/>
-      <c r="B109" s="168"/>
-      <c r="C109" s="129"/>
-      <c r="D109" s="168"/>
-      <c r="E109" s="129"/>
-      <c r="F109" s="131"/>
+      <c r="A109" s="72"/>
+      <c r="B109" s="183"/>
+      <c r="C109" s="72"/>
+      <c r="D109" s="183"/>
+      <c r="E109" s="72"/>
+      <c r="F109" s="74"/>
     </row>
     <row r="110" spans="1:6" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="129"/>
-      <c r="B110" s="168"/>
-      <c r="C110" s="129"/>
-      <c r="D110" s="168"/>
-      <c r="E110" s="129"/>
-      <c r="F110" s="131"/>
+      <c r="A110" s="72"/>
+      <c r="B110" s="183"/>
+      <c r="C110" s="72"/>
+      <c r="D110" s="183"/>
+      <c r="E110" s="72"/>
+      <c r="F110" s="74"/>
     </row>
     <row r="111" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="129"/>
-      <c r="B111" s="168"/>
-      <c r="C111" s="129"/>
-      <c r="D111" s="168"/>
-      <c r="E111" s="129"/>
-      <c r="F111" s="131"/>
+      <c r="A111" s="72"/>
+      <c r="B111" s="183"/>
+      <c r="C111" s="72"/>
+      <c r="D111" s="183"/>
+      <c r="E111" s="72"/>
+      <c r="F111" s="74"/>
     </row>
     <row r="112" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="184"/>
@@ -40008,154 +40008,154 @@
       <c r="F112" s="186"/>
     </row>
     <row r="113" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="165" t="s">
+      <c r="A113" s="167" t="s">
         <v>75</v>
       </c>
-      <c r="B113" s="178"/>
-      <c r="C113" s="165" t="s">
+      <c r="B113" s="171"/>
+      <c r="C113" s="167" t="s">
         <v>97</v>
       </c>
-      <c r="D113" s="178"/>
-      <c r="E113" s="183" t="s">
+      <c r="D113" s="171"/>
+      <c r="E113" s="181" t="s">
         <v>76</v>
       </c>
-      <c r="F113" s="178"/>
+      <c r="F113" s="171"/>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="167"/>
-      <c r="B114" s="168"/>
-      <c r="C114" s="167"/>
-      <c r="D114" s="168"/>
-      <c r="E114" s="167"/>
-      <c r="F114" s="131"/>
+      <c r="A114" s="182"/>
+      <c r="B114" s="183"/>
+      <c r="C114" s="182"/>
+      <c r="D114" s="183"/>
+      <c r="E114" s="182"/>
+      <c r="F114" s="74"/>
     </row>
     <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="129"/>
-      <c r="B115" s="168"/>
-      <c r="C115" s="129"/>
-      <c r="D115" s="168"/>
-      <c r="E115" s="129"/>
-      <c r="F115" s="131"/>
+      <c r="A115" s="72"/>
+      <c r="B115" s="183"/>
+      <c r="C115" s="72"/>
+      <c r="D115" s="183"/>
+      <c r="E115" s="72"/>
+      <c r="F115" s="74"/>
     </row>
     <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="129"/>
-      <c r="B116" s="168"/>
-      <c r="C116" s="129"/>
-      <c r="D116" s="168"/>
-      <c r="E116" s="129"/>
-      <c r="F116" s="131"/>
+      <c r="A116" s="72"/>
+      <c r="B116" s="183"/>
+      <c r="C116" s="72"/>
+      <c r="D116" s="183"/>
+      <c r="E116" s="72"/>
+      <c r="F116" s="74"/>
     </row>
     <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="129"/>
-      <c r="B117" s="168"/>
-      <c r="C117" s="129"/>
-      <c r="D117" s="168"/>
-      <c r="E117" s="129"/>
-      <c r="F117" s="131"/>
+      <c r="A117" s="72"/>
+      <c r="B117" s="183"/>
+      <c r="C117" s="72"/>
+      <c r="D117" s="183"/>
+      <c r="E117" s="72"/>
+      <c r="F117" s="74"/>
     </row>
     <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="129"/>
-      <c r="B118" s="168"/>
-      <c r="C118" s="129"/>
-      <c r="D118" s="168"/>
-      <c r="E118" s="129"/>
-      <c r="F118" s="131"/>
+      <c r="A118" s="72"/>
+      <c r="B118" s="183"/>
+      <c r="C118" s="72"/>
+      <c r="D118" s="183"/>
+      <c r="E118" s="72"/>
+      <c r="F118" s="74"/>
     </row>
     <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="129"/>
-      <c r="B119" s="168"/>
-      <c r="C119" s="129"/>
-      <c r="D119" s="168"/>
-      <c r="E119" s="129"/>
-      <c r="F119" s="131"/>
+      <c r="A119" s="72"/>
+      <c r="B119" s="183"/>
+      <c r="C119" s="72"/>
+      <c r="D119" s="183"/>
+      <c r="E119" s="72"/>
+      <c r="F119" s="74"/>
     </row>
     <row r="120" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="129"/>
-      <c r="B120" s="168"/>
-      <c r="C120" s="129"/>
-      <c r="D120" s="168"/>
-      <c r="E120" s="129"/>
-      <c r="F120" s="131"/>
+      <c r="A120" s="72"/>
+      <c r="B120" s="183"/>
+      <c r="C120" s="72"/>
+      <c r="D120" s="183"/>
+      <c r="E120" s="72"/>
+      <c r="F120" s="74"/>
     </row>
     <row r="121" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="129"/>
-      <c r="B121" s="168"/>
-      <c r="C121" s="129"/>
-      <c r="D121" s="168"/>
-      <c r="E121" s="129"/>
-      <c r="F121" s="131"/>
+      <c r="A121" s="72"/>
+      <c r="B121" s="183"/>
+      <c r="C121" s="72"/>
+      <c r="D121" s="183"/>
+      <c r="E121" s="72"/>
+      <c r="F121" s="74"/>
     </row>
     <row r="122" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="129"/>
-      <c r="B122" s="168"/>
-      <c r="C122" s="129"/>
-      <c r="D122" s="168"/>
-      <c r="E122" s="129"/>
-      <c r="F122" s="131"/>
+      <c r="A122" s="72"/>
+      <c r="B122" s="183"/>
+      <c r="C122" s="72"/>
+      <c r="D122" s="183"/>
+      <c r="E122" s="72"/>
+      <c r="F122" s="74"/>
     </row>
     <row r="123" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="129"/>
-      <c r="B123" s="168"/>
-      <c r="C123" s="129"/>
-      <c r="D123" s="168"/>
-      <c r="E123" s="129"/>
-      <c r="F123" s="131"/>
+      <c r="A123" s="72"/>
+      <c r="B123" s="183"/>
+      <c r="C123" s="72"/>
+      <c r="D123" s="183"/>
+      <c r="E123" s="72"/>
+      <c r="F123" s="74"/>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="129"/>
-      <c r="B124" s="168"/>
-      <c r="C124" s="129"/>
-      <c r="D124" s="168"/>
-      <c r="E124" s="129"/>
-      <c r="F124" s="131"/>
+      <c r="A124" s="72"/>
+      <c r="B124" s="183"/>
+      <c r="C124" s="72"/>
+      <c r="D124" s="183"/>
+      <c r="E124" s="72"/>
+      <c r="F124" s="74"/>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="129"/>
-      <c r="B125" s="168"/>
-      <c r="C125" s="129"/>
-      <c r="D125" s="168"/>
-      <c r="E125" s="129"/>
-      <c r="F125" s="131"/>
+      <c r="A125" s="72"/>
+      <c r="B125" s="183"/>
+      <c r="C125" s="72"/>
+      <c r="D125" s="183"/>
+      <c r="E125" s="72"/>
+      <c r="F125" s="74"/>
     </row>
     <row r="126" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="129"/>
-      <c r="B126" s="168"/>
-      <c r="C126" s="129"/>
-      <c r="D126" s="168"/>
-      <c r="E126" s="129"/>
-      <c r="F126" s="131"/>
+      <c r="A126" s="72"/>
+      <c r="B126" s="183"/>
+      <c r="C126" s="72"/>
+      <c r="D126" s="183"/>
+      <c r="E126" s="72"/>
+      <c r="F126" s="74"/>
     </row>
     <row r="127" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="129"/>
-      <c r="B127" s="168"/>
-      <c r="C127" s="129"/>
-      <c r="D127" s="168"/>
-      <c r="E127" s="129"/>
-      <c r="F127" s="131"/>
+      <c r="A127" s="72"/>
+      <c r="B127" s="183"/>
+      <c r="C127" s="72"/>
+      <c r="D127" s="183"/>
+      <c r="E127" s="72"/>
+      <c r="F127" s="74"/>
     </row>
     <row r="128" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="129"/>
-      <c r="B128" s="168"/>
-      <c r="C128" s="129"/>
-      <c r="D128" s="168"/>
-      <c r="E128" s="129"/>
-      <c r="F128" s="131"/>
+      <c r="A128" s="72"/>
+      <c r="B128" s="183"/>
+      <c r="C128" s="72"/>
+      <c r="D128" s="183"/>
+      <c r="E128" s="72"/>
+      <c r="F128" s="74"/>
     </row>
     <row r="129" spans="1:7" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="129"/>
-      <c r="B129" s="168"/>
-      <c r="C129" s="129"/>
-      <c r="D129" s="168"/>
-      <c r="E129" s="129"/>
-      <c r="F129" s="131"/>
+      <c r="A129" s="72"/>
+      <c r="B129" s="183"/>
+      <c r="C129" s="72"/>
+      <c r="D129" s="183"/>
+      <c r="E129" s="72"/>
+      <c r="F129" s="74"/>
     </row>
     <row r="130" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="129"/>
-      <c r="B130" s="168"/>
-      <c r="C130" s="129"/>
-      <c r="D130" s="168"/>
-      <c r="E130" s="129"/>
-      <c r="F130" s="131"/>
+      <c r="A130" s="72"/>
+      <c r="B130" s="183"/>
+      <c r="C130" s="72"/>
+      <c r="D130" s="183"/>
+      <c r="E130" s="72"/>
+      <c r="F130" s="74"/>
     </row>
     <row r="131" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="184"/>
@@ -40166,41 +40166,41 @@
       <c r="F131" s="186"/>
     </row>
     <row r="132" spans="1:7" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="165" t="s">
+      <c r="A132" s="167" t="s">
         <v>67</v>
       </c>
-      <c r="B132" s="177"/>
-      <c r="C132" s="177"/>
-      <c r="D132" s="177"/>
-      <c r="E132" s="177"/>
-      <c r="F132" s="178"/>
+      <c r="B132" s="187"/>
+      <c r="C132" s="187"/>
+      <c r="D132" s="187"/>
+      <c r="E132" s="187"/>
+      <c r="F132" s="171"/>
     </row>
     <row r="133" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="181" t="s">
+      <c r="A133" s="172" t="s">
         <v>68</v>
       </c>
-      <c r="B133" s="182"/>
-      <c r="C133" s="170"/>
-      <c r="D133" s="193">
+      <c r="B133" s="175"/>
+      <c r="C133" s="173"/>
+      <c r="D133" s="174">
         <f>C2</f>
         <v>0</v>
       </c>
-      <c r="E133" s="182"/>
-      <c r="F133" s="170"/>
+      <c r="E133" s="175"/>
+      <c r="F133" s="173"/>
     </row>
     <row r="134" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="211" t="s">
+      <c r="A134" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="B134" s="209"/>
-      <c r="C134" s="208" t="s">
+      <c r="B134" s="201"/>
+      <c r="C134" s="198" t="s">
         <v>78</v>
       </c>
-      <c r="D134" s="209"/>
-      <c r="E134" s="208" t="s">
+      <c r="D134" s="201"/>
+      <c r="E134" s="198" t="s">
         <v>79</v>
       </c>
-      <c r="F134" s="210"/>
+      <c r="F134" s="199"/>
       <c r="G134" s="20"/>
     </row>
     <row r="135" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -40335,8 +40335,8 @@
         <f>'DATOS GENERALES'!M33</f>
         <v>0</v>
       </c>
-      <c r="C141" s="206"/>
-      <c r="D141" s="207"/>
+      <c r="C141" s="213"/>
+      <c r="D141" s="214"/>
       <c r="E141" s="60" t="s">
         <v>144</v>
       </c>
@@ -40393,46 +40393,46 @@
       <c r="G145" s="20"/>
     </row>
     <row r="146" spans="1:26" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="203" t="s">
+      <c r="A146" s="210" t="s">
         <v>58</v>
       </c>
-      <c r="B146" s="204"/>
-      <c r="C146" s="204"/>
-      <c r="D146" s="204"/>
-      <c r="E146" s="204"/>
-      <c r="F146" s="205"/>
+      <c r="B146" s="211"/>
+      <c r="C146" s="211"/>
+      <c r="D146" s="211"/>
+      <c r="E146" s="211"/>
+      <c r="F146" s="212"/>
     </row>
     <row r="147" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="195"/>
-      <c r="B147" s="196"/>
-      <c r="C147" s="196"/>
-      <c r="D147" s="196"/>
-      <c r="E147" s="196"/>
-      <c r="F147" s="197"/>
+      <c r="A147" s="202"/>
+      <c r="B147" s="203"/>
+      <c r="C147" s="203"/>
+      <c r="D147" s="203"/>
+      <c r="E147" s="203"/>
+      <c r="F147" s="204"/>
     </row>
     <row r="148" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="179"/>
-      <c r="B148" s="198"/>
-      <c r="C148" s="198"/>
-      <c r="D148" s="198"/>
-      <c r="E148" s="198"/>
-      <c r="F148" s="199"/>
+      <c r="A148" s="188"/>
+      <c r="B148" s="205"/>
+      <c r="C148" s="205"/>
+      <c r="D148" s="205"/>
+      <c r="E148" s="205"/>
+      <c r="F148" s="206"/>
     </row>
     <row r="149" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="179"/>
-      <c r="B149" s="198"/>
-      <c r="C149" s="198"/>
-      <c r="D149" s="198"/>
-      <c r="E149" s="198"/>
-      <c r="F149" s="199"/>
+      <c r="A149" s="188"/>
+      <c r="B149" s="205"/>
+      <c r="C149" s="205"/>
+      <c r="D149" s="205"/>
+      <c r="E149" s="205"/>
+      <c r="F149" s="206"/>
     </row>
     <row r="150" spans="1:26" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="200"/>
-      <c r="B150" s="201"/>
-      <c r="C150" s="201"/>
-      <c r="D150" s="201"/>
-      <c r="E150" s="201"/>
-      <c r="F150" s="202"/>
+      <c r="A150" s="207"/>
+      <c r="B150" s="208"/>
+      <c r="C150" s="208"/>
+      <c r="D150" s="208"/>
+      <c r="E150" s="208"/>
+      <c r="F150" s="209"/>
     </row>
     <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19"/>
@@ -47904,6 +47904,44 @@
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="A147:F150"/>
+    <mergeCell ref="A146:F146"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="A58:B74"/>
+    <mergeCell ref="C58:D74"/>
+    <mergeCell ref="E58:F74"/>
+    <mergeCell ref="A114:B131"/>
+    <mergeCell ref="C114:D131"/>
+    <mergeCell ref="E114:F131"/>
+    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="A40:B56"/>
+    <mergeCell ref="C40:D56"/>
+    <mergeCell ref="E40:F56"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B38"/>
+    <mergeCell ref="C22:D38"/>
+    <mergeCell ref="E22:F38"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="A95:B112"/>
+    <mergeCell ref="C95:D112"/>
+    <mergeCell ref="E95:F112"/>
+    <mergeCell ref="A113:B113"/>
     <mergeCell ref="C76:D93"/>
     <mergeCell ref="E76:F93"/>
     <mergeCell ref="B1:E1"/>
@@ -47920,44 +47958,6 @@
     <mergeCell ref="C4:D20"/>
     <mergeCell ref="E4:F20"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="A134:B134"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="A95:B112"/>
-    <mergeCell ref="C95:D112"/>
-    <mergeCell ref="E95:F112"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B38"/>
-    <mergeCell ref="C22:D38"/>
-    <mergeCell ref="E22:F38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="A40:B56"/>
-    <mergeCell ref="C40:D56"/>
-    <mergeCell ref="E40:F56"/>
-    <mergeCell ref="A147:F150"/>
-    <mergeCell ref="A146:F146"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="A58:B74"/>
-    <mergeCell ref="C58:D74"/>
-    <mergeCell ref="E58:F74"/>
-    <mergeCell ref="A114:B131"/>
-    <mergeCell ref="C114:D131"/>
-    <mergeCell ref="E114:F131"/>
-    <mergeCell ref="A132:F132"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="C134:D134"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
@@ -47981,245 +47981,245 @@
   <sheetData>
     <row r="1" spans="1:6" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9"/>
-      <c r="B1" s="189" t="s">
+      <c r="B1" s="166" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
       <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="167" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="190"/>
-      <c r="C2" s="165">
-        <f>'MEDICIONES DE ENTRADA '!C2</f>
+      <c r="B2" s="168"/>
+      <c r="C2" s="167">
+        <f>'MEDICIONES DE ENTRADA'!C2</f>
         <v>0</v>
       </c>
-      <c r="D2" s="155"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="170"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="173"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="165" t="s">
+      <c r="A3" s="167" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="191"/>
-      <c r="C3" s="165" t="s">
+      <c r="B3" s="169"/>
+      <c r="C3" s="167" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="220"/>
-      <c r="E3" s="217" t="s">
+      <c r="D3" s="221"/>
+      <c r="E3" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="F3" s="221"/>
+      <c r="F3" s="222"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="214"/>
-      <c r="B4" s="128"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="216"/>
-      <c r="F4" s="131"/>
+      <c r="A4" s="215"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="215"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="217"/>
+      <c r="F4" s="74"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="215"/>
-      <c r="B5" s="131"/>
-      <c r="C5" s="215"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="215"/>
-      <c r="F5" s="131"/>
+      <c r="A5" s="216"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="74"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="215"/>
-      <c r="B6" s="131"/>
-      <c r="C6" s="215"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="215"/>
-      <c r="F6" s="131"/>
+      <c r="A6" s="216"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="216"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="74"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="215"/>
-      <c r="B7" s="131"/>
-      <c r="C7" s="215"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="215"/>
-      <c r="F7" s="131"/>
+      <c r="A7" s="216"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="216"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="216"/>
+      <c r="F7" s="74"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="215"/>
-      <c r="B8" s="131"/>
-      <c r="C8" s="215"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="215"/>
-      <c r="F8" s="131"/>
+      <c r="A8" s="216"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="216"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="216"/>
+      <c r="F8" s="74"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="215"/>
-      <c r="B9" s="131"/>
-      <c r="C9" s="215"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="215"/>
-      <c r="F9" s="131"/>
+      <c r="A9" s="216"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="216"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="74"/>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="215"/>
-      <c r="B10" s="131"/>
-      <c r="C10" s="215"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="131"/>
+      <c r="A10" s="216"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="216"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="216"/>
+      <c r="F10" s="74"/>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="215"/>
-      <c r="B11" s="131"/>
-      <c r="C11" s="215"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="215"/>
-      <c r="F11" s="131"/>
+      <c r="A11" s="216"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="216"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="216"/>
+      <c r="F11" s="74"/>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="215"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="215"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="215"/>
-      <c r="F12" s="131"/>
+      <c r="A12" s="216"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="216"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="216"/>
+      <c r="F12" s="74"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="215"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="215"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="215"/>
-      <c r="F13" s="131"/>
+      <c r="A13" s="216"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="216"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="216"/>
+      <c r="F13" s="74"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="215"/>
-      <c r="B14" s="131"/>
-      <c r="C14" s="215"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="215"/>
-      <c r="F14" s="131"/>
+      <c r="A14" s="216"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="216"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="216"/>
+      <c r="F14" s="74"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="215"/>
-      <c r="B15" s="131"/>
-      <c r="C15" s="215"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="215"/>
-      <c r="F15" s="131"/>
+      <c r="A15" s="216"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="216"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="216"/>
+      <c r="F15" s="74"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="215"/>
-      <c r="B16" s="131"/>
-      <c r="C16" s="215"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="215"/>
-      <c r="F16" s="131"/>
+      <c r="A16" s="216"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="216"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="216"/>
+      <c r="F16" s="74"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="215"/>
-      <c r="B17" s="131"/>
-      <c r="C17" s="215"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="215"/>
-      <c r="F17" s="131"/>
+      <c r="A17" s="216"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="216"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="216"/>
+      <c r="F17" s="74"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="215"/>
-      <c r="B18" s="131"/>
-      <c r="C18" s="215"/>
-      <c r="D18" s="131"/>
-      <c r="E18" s="215"/>
-      <c r="F18" s="131"/>
+      <c r="A18" s="216"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="216"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="216"/>
+      <c r="F18" s="74"/>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="215"/>
-      <c r="B19" s="131"/>
-      <c r="C19" s="215"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="215"/>
-      <c r="F19" s="131"/>
+      <c r="A19" s="216"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="216"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="216"/>
+      <c r="F19" s="74"/>
     </row>
     <row r="20" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="215"/>
-      <c r="B20" s="131"/>
-      <c r="C20" s="215"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="215"/>
-      <c r="F20" s="131"/>
+      <c r="A20" s="216"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="216"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="216"/>
+      <c r="F20" s="74"/>
     </row>
     <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="228" t="s">
+      <c r="A21" s="229" t="s">
         <v>112</v>
       </c>
-      <c r="B21" s="230" t="s">
+      <c r="B21" s="231" t="s">
         <v>113</v>
       </c>
       <c r="C21" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="222"/>
-      <c r="E21" s="223"/>
-      <c r="F21" s="224"/>
+      <c r="D21" s="223"/>
+      <c r="E21" s="224"/>
+      <c r="F21" s="225"/>
     </row>
     <row r="22" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="229"/>
-      <c r="B22" s="231"/>
+      <c r="A22" s="230"/>
+      <c r="B22" s="232"/>
       <c r="C22" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="D22" s="225"/>
-      <c r="E22" s="226"/>
-      <c r="F22" s="227"/>
+      <c r="D22" s="226"/>
+      <c r="E22" s="227"/>
+      <c r="F22" s="228"/>
     </row>
     <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="217" t="s">
+      <c r="A23" s="218" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="218"/>
-      <c r="C23" s="218"/>
-      <c r="D23" s="218"/>
-      <c r="E23" s="218"/>
-      <c r="F23" s="219"/>
+      <c r="B23" s="219"/>
+      <c r="C23" s="219"/>
+      <c r="D23" s="219"/>
+      <c r="E23" s="219"/>
+      <c r="F23" s="220"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="179">
+      <c r="A24" s="188">
         <f>NOVEDADES!A94</f>
         <v>0</v>
       </c>
-      <c r="B24" s="130"/>
-      <c r="C24" s="130"/>
-      <c r="D24" s="130"/>
-      <c r="E24" s="130"/>
-      <c r="F24" s="131"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="74"/>
     </row>
     <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="179"/>
-      <c r="B25" s="130"/>
-      <c r="C25" s="130"/>
-      <c r="D25" s="130"/>
-      <c r="E25" s="130"/>
-      <c r="F25" s="131"/>
+      <c r="A25" s="188"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="74"/>
     </row>
     <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="129"/>
-      <c r="B26" s="130"/>
-      <c r="C26" s="130"/>
-      <c r="D26" s="130"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="131"/>
+      <c r="A26" s="72"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="74"/>
     </row>
     <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="132"/>
-      <c r="B27" s="133"/>
-      <c r="C27" s="133"/>
-      <c r="D27" s="133"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="134"/>
+      <c r="A27" s="75"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="77"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19"/>
